--- a/data/parts_report_future.xlsx
+++ b/data/parts_report_future.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb12da676b4e44d97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Ra9d332283a3141bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R24a6892935784ec7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="R64927772b50f4963"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -228,21 +228,21 @@
         </x:is>
       </x:c>
       <x:c r="B3" t="n" s="5">
-        <x:v>294.96</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C3" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, Club Member, Club Member (Additional System), MULTI- 2, Parts Ordered, Trane Supply</x:t>
+          <x:t>10-10-10, Club Member, Parts Ordered, Trane Supply</x:t>
         </x:is>
       </x:c>
       <x:c r="D3" t="inlineStr" s="9">
         <x:is>
-          <x:t>554624809</x:t>
+          <x:t>586864800</x:t>
         </x:is>
       </x:c>
       <x:c r="E3" t="inlineStr" s="11">
         <x:is>
-          <x:t>554624809</x:t>
+          <x:t>586864800</x:t>
         </x:is>
       </x:c>
       <x:c r="F3" s="13">
@@ -250,7 +250,7 @@
       </x:c>
       <x:c r="G3" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Carlos Machado</x:t>
+          <x:t>PP David Escobar</x:t>
         </x:is>
       </x:c>
       <x:c r="H3" t="inlineStr" s="17">
@@ -265,14 +265,14 @@
       </x:c>
       <x:c r="J3" t="inlineStr" s="21">
         <x:is>
-          <x:t>Michael &amp; Delle Lenzen</x:t>
+          <x:t>Hope Gadea</x:t>
         </x:is>
       </x:c>
       <x:c r="K3" s="23">
-        <x:v>45996</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="L3" s="25">
-        <x:v>45996</x:v>
+        <x:v>46100</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -282,21 +282,21 @@
         </x:is>
       </x:c>
       <x:c r="B4" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>294.96</x:v>
       </x:c>
       <x:c r="C4" t="inlineStr" s="7">
         <x:is>
-          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member 3 sys, Gemaire, MULTI- 3, Parts Ordered</x:t>
+          <x:t>10-10-10, 10-10-10, Club Member, Club Member (Additional System), MULTI- 2, Parts Ordered, Trane Supply</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" t="inlineStr" s="9">
         <x:is>
-          <x:t>586595677</x:t>
+          <x:t>554624809</x:t>
         </x:is>
       </x:c>
       <x:c r="E4" t="inlineStr" s="11">
         <x:is>
-          <x:t>586595677</x:t>
+          <x:t>554624809</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" s="13">
@@ -304,7 +304,7 @@
       </x:c>
       <x:c r="G4" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
+          <x:t>PP Carlos Machado</x:t>
         </x:is>
       </x:c>
       <x:c r="H4" t="inlineStr" s="17">
@@ -314,19 +314,19 @@
       </x:c>
       <x:c r="I4" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J4" t="inlineStr" s="21">
         <x:is>
-          <x:t>Bob Lauson</x:t>
+          <x:t>Michael &amp; Delle Lenzen</x:t>
         </x:is>
       </x:c>
       <x:c r="K4" s="23">
-        <x:v>46098</x:v>
+        <x:v>45996</x:v>
       </x:c>
       <x:c r="L4" s="25">
-        <x:v>46098</x:v>
+        <x:v>45996</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -336,21 +336,21 @@
         </x:is>
       </x:c>
       <x:c r="B5" t="n" s="5">
-        <x:v>1340.1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C5" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Club Member (Additional System), Gemaire, MULTI- 3, Parts Received , PLM</x:t>
+          <x:t>Club Member, LW- 2 YEAR LABOR, Parts Ordered, Trane Supply</x:t>
         </x:is>
       </x:c>
       <x:c r="D5" t="inlineStr" s="9">
         <x:is>
-          <x:t>587281524</x:t>
+          <x:t>587077196</x:t>
         </x:is>
       </x:c>
       <x:c r="E5" t="inlineStr" s="11">
         <x:is>
-          <x:t>587281524</x:t>
+          <x:t>587077196</x:t>
         </x:is>
       </x:c>
       <x:c r="F5" s="13">
@@ -358,7 +358,7 @@
       </x:c>
       <x:c r="G5" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
+          <x:t>Tyler Gallatin</x:t>
         </x:is>
       </x:c>
       <x:c r="H5" t="inlineStr" s="17">
@@ -368,19 +368,19 @@
       </x:c>
       <x:c r="I5" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J5" t="inlineStr" s="21">
         <x:is>
-          <x:t>Robert Lake</x:t>
+          <x:t>Timberwalk Association Inc</x:t>
         </x:is>
       </x:c>
       <x:c r="K5" s="23">
-        <x:v>46105</x:v>
+        <x:v>46102</x:v>
       </x:c>
       <x:c r="L5" s="25">
-        <x:v>46105</x:v>
+        <x:v>46102</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -390,21 +390,21 @@
         </x:is>
       </x:c>
       <x:c r="B6" t="n" s="5">
-        <x:v>3247.45</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C6" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, Club Member, Club Member 2 sys , Gemaire, Parts Received , PLM</x:t>
+          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member 3 sys, Gemaire, MULTI- 3, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D6" t="inlineStr" s="9">
         <x:is>
-          <x:t>587314216</x:t>
+          <x:t>586595677</x:t>
         </x:is>
       </x:c>
       <x:c r="E6" t="inlineStr" s="11">
         <x:is>
-          <x:t>587314216</x:t>
+          <x:t>586595677</x:t>
         </x:is>
       </x:c>
       <x:c r="F6" s="13">
@@ -412,7 +412,7 @@
       </x:c>
       <x:c r="G6" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t>PP Alejandro Espinosa</x:t>
         </x:is>
       </x:c>
       <x:c r="H6" t="inlineStr" s="17">
@@ -422,19 +422,19 @@
       </x:c>
       <x:c r="I6" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J6" t="inlineStr" s="21">
         <x:is>
-          <x:t>FRIEDMAN, SAMANTHA</x:t>
+          <x:t>Bob Lauson</x:t>
         </x:is>
       </x:c>
       <x:c r="K6" s="23">
-        <x:v>46105</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="L6" s="25">
-        <x:v>46105</x:v>
+        <x:v>46098</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -444,21 +444,21 @@
         </x:is>
       </x:c>
       <x:c r="B7" t="n" s="5">
-        <x:v>292.95</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C7" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Club Member, Parts Ordered, PLM</x:t>
+          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Goodman distribution , MULTI- 5, Parts Ordered, PLM, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D7" t="inlineStr" s="9">
         <x:is>
-          <x:t>587301961</x:t>
+          <x:t>587266021</x:t>
         </x:is>
       </x:c>
       <x:c r="E7" t="inlineStr" s="11">
         <x:is>
-          <x:t>587301961</x:t>
+          <x:t>587266021</x:t>
         </x:is>
       </x:c>
       <x:c r="F7" s="13">
@@ -466,7 +466,7 @@
       </x:c>
       <x:c r="G7" t="inlineStr" s="15">
         <x:is>
-          <x:t>Jesse Dague</x:t>
+          <x:t>PP Cesar Levy</x:t>
         </x:is>
       </x:c>
       <x:c r="H7" t="inlineStr" s="17">
@@ -476,12 +476,12 @@
       </x:c>
       <x:c r="I7" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J7" t="inlineStr" s="21">
         <x:is>
-          <x:t>CHACON, LERA</x:t>
+          <x:t>Nevalee &amp; Paul Oneil</x:t>
         </x:is>
       </x:c>
       <x:c r="K7" s="23">
@@ -498,29 +498,29 @@
         </x:is>
       </x:c>
       <x:c r="B8" t="n" s="5">
-        <x:v>289.85</x:v>
+        <x:v>1340.1</x:v>
       </x:c>
       <x:c r="C8" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
+          <x:t>Club Member, Club Member (Additional System), Gemaire, MULTI- 3, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D8" t="inlineStr" s="9">
         <x:is>
-          <x:t>587426826</x:t>
+          <x:t>587281524</x:t>
         </x:is>
       </x:c>
       <x:c r="E8" t="inlineStr" s="11">
         <x:is>
-          <x:t>587426826</x:t>
+          <x:t>587281524</x:t>
         </x:is>
       </x:c>
       <x:c r="F8" s="13">
-        <x:v>46108</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="G8" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t>PP Alejandro Espinosa</x:t>
         </x:is>
       </x:c>
       <x:c r="H8" t="inlineStr" s="17">
@@ -530,19 +530,19 @@
       </x:c>
       <x:c r="I8" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J8" t="inlineStr" s="21">
         <x:is>
-          <x:t>Bill Esposito</x:t>
+          <x:t>Robert Lake</x:t>
         </x:is>
       </x:c>
       <x:c r="K8" s="23">
-        <x:v>46106</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L8" s="25">
-        <x:v>46106</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -552,29 +552,29 @@
         </x:is>
       </x:c>
       <x:c r="B9" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>3247.45</x:v>
       </x:c>
       <x:c r="C9" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Received </x:t>
+          <x:t>10-Year Labor, Club Member, Club Member 2 sys , Gemaire, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D9" t="inlineStr" s="9">
         <x:is>
-          <x:t>583339941</x:t>
+          <x:t>587314216</x:t>
         </x:is>
       </x:c>
       <x:c r="E9" t="inlineStr" s="11">
         <x:is>
-          <x:t>583339941</x:t>
+          <x:t>587314216</x:t>
         </x:is>
       </x:c>
       <x:c r="F9" s="13">
-        <x:v>46108</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="G9" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rickey McClam </x:t>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H9" t="inlineStr" s="17">
@@ -589,14 +589,14 @@
       </x:c>
       <x:c r="J9" t="inlineStr" s="21">
         <x:is>
-          <x:t>Walter Lizarbe</x:t>
+          <x:t>FRIEDMAN, SAMANTHA</x:t>
         </x:is>
       </x:c>
       <x:c r="K9" s="23">
-        <x:v>46071</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L9" s="25">
-        <x:v>46083</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -606,29 +606,29 @@
         </x:is>
       </x:c>
       <x:c r="B10" t="n" s="5">
-        <x:v>1248.8</x:v>
+        <x:v>292.95</x:v>
       </x:c>
       <x:c r="C10" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Lennox Supply, Parts Ordered</x:t>
+          <x:t>Baker Supply, Club Member, Parts Ordered, PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D10" t="inlineStr" s="9">
         <x:is>
-          <x:t>587303898</x:t>
+          <x:t>587301961</x:t>
         </x:is>
       </x:c>
       <x:c r="E10" t="inlineStr" s="11">
         <x:is>
-          <x:t>587303898</x:t>
+          <x:t>587301961</x:t>
         </x:is>
       </x:c>
       <x:c r="F10" s="13">
-        <x:v>46108</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="G10" t="inlineStr" s="15">
         <x:is>
-          <x:t>Xavier Mateo</x:t>
+          <x:t>Jesse Dague</x:t>
         </x:is>
       </x:c>
       <x:c r="H10" t="inlineStr" s="17">
@@ -643,7 +643,7 @@
       </x:c>
       <x:c r="J10" t="inlineStr" s="21">
         <x:is>
-          <x:t>ROBERT MCCABE</x:t>
+          <x:t>CHACON, LERA</x:t>
         </x:is>
       </x:c>
       <x:c r="K10" s="23">
@@ -660,21 +660,21 @@
         </x:is>
       </x:c>
       <x:c r="B11" t="n" s="5">
-        <x:v>1267.95</x:v>
+        <x:v>289.85</x:v>
       </x:c>
       <x:c r="C11" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member 3 sys, Gemaire, Parts Ordered</x:t>
+          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D11" t="inlineStr" s="9">
         <x:is>
-          <x:t>578585007</x:t>
+          <x:t>587426826</x:t>
         </x:is>
       </x:c>
       <x:c r="E11" t="inlineStr" s="11">
         <x:is>
-          <x:t>578585007</x:t>
+          <x:t>587426826</x:t>
         </x:is>
       </x:c>
       <x:c r="F11" s="13">
@@ -682,7 +682,7 @@
       </x:c>
       <x:c r="G11" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Cesar Levy</x:t>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H11" t="inlineStr" s="17">
@@ -697,14 +697,14 @@
       </x:c>
       <x:c r="J11" t="inlineStr" s="21">
         <x:is>
-          <x:t>Serghei Arsentiev</x:t>
+          <x:t>Bill Esposito</x:t>
         </x:is>
       </x:c>
       <x:c r="K11" s="23">
-        <x:v>46037</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L11" s="25">
-        <x:v>46037</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -718,17 +718,17 @@
       </x:c>
       <x:c r="C12" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, PLM, Potential Member</x:t>
+          <x:t>Carrier enterprise, Club Member, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D12" t="inlineStr" s="9">
         <x:is>
-          <x:t>583259145</x:t>
+          <x:t>583339941</x:t>
         </x:is>
       </x:c>
       <x:c r="E12" t="inlineStr" s="11">
         <x:is>
-          <x:t>583259145</x:t>
+          <x:t>583339941</x:t>
         </x:is>
       </x:c>
       <x:c r="F12" s="13">
@@ -736,7 +736,7 @@
       </x:c>
       <x:c r="G12" t="inlineStr" s="15">
         <x:is>
-          <x:t/>
+          <x:t>Rickey McClam </x:t>
         </x:is>
       </x:c>
       <x:c r="H12" t="inlineStr" s="17">
@@ -751,14 +751,14 @@
       </x:c>
       <x:c r="J12" t="inlineStr" s="21">
         <x:is>
-          <x:t>John Moore</x:t>
+          <x:t>Walter Lizarbe</x:t>
         </x:is>
       </x:c>
       <x:c r="K12" s="23">
-        <x:v>46070</x:v>
+        <x:v>46071</x:v>
       </x:c>
       <x:c r="L12" s="25">
-        <x:v>46070</x:v>
+        <x:v>46083</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -768,21 +768,21 @@
         </x:is>
       </x:c>
       <x:c r="B13" t="n" s="5">
-        <x:v>2405.92</x:v>
+        <x:v>1248.8</x:v>
       </x:c>
       <x:c r="C13" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Parts Ordered, Potential Member</x:t>
+          <x:t>Club Member, Lennox Supply, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D13" t="inlineStr" s="9">
         <x:is>
-          <x:t>578394047</x:t>
+          <x:t>587303898</x:t>
         </x:is>
       </x:c>
       <x:c r="E13" t="inlineStr" s="11">
         <x:is>
-          <x:t>578394047</x:t>
+          <x:t>587303898</x:t>
         </x:is>
       </x:c>
       <x:c r="F13" s="13">
@@ -790,7 +790,7 @@
       </x:c>
       <x:c r="G13" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Gurpreet Parihar</x:t>
+          <x:t>Xavier Mateo</x:t>
         </x:is>
       </x:c>
       <x:c r="H13" t="inlineStr" s="17">
@@ -800,19 +800,19 @@
       </x:c>
       <x:c r="I13" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J13" t="inlineStr" s="21">
         <x:is>
-          <x:t>Edgar Irving</x:t>
+          <x:t>ROBERT MCCABE</x:t>
         </x:is>
       </x:c>
       <x:c r="K13" s="23">
-        <x:v>46036</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L13" s="25">
-        <x:v>46036</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -822,21 +822,21 @@
         </x:is>
       </x:c>
       <x:c r="B14" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1267.95</x:v>
       </x:c>
       <x:c r="C14" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Club Member, Goodman distribution , Parts Ordered</x:t>
+          <x:t>Club Member 3 sys, Gemaire, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D14" t="inlineStr" s="9">
         <x:is>
-          <x:t>585388429</x:t>
+          <x:t>578585007</x:t>
         </x:is>
       </x:c>
       <x:c r="E14" t="inlineStr" s="11">
         <x:is>
-          <x:t>585388429</x:t>
+          <x:t>578585007</x:t>
         </x:is>
       </x:c>
       <x:c r="F14" s="13">
@@ -844,7 +844,7 @@
       </x:c>
       <x:c r="G14" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rickey McClam </x:t>
+          <x:t>PP Cesar Levy</x:t>
         </x:is>
       </x:c>
       <x:c r="H14" t="inlineStr" s="17">
@@ -859,14 +859,14 @@
       </x:c>
       <x:c r="J14" t="inlineStr" s="21">
         <x:is>
-          <x:t>Charles Funkey</x:t>
+          <x:t>Serghei Arsentiev</x:t>
         </x:is>
       </x:c>
       <x:c r="K14" s="23">
-        <x:v>46086</x:v>
+        <x:v>46037</x:v>
       </x:c>
       <x:c r="L14" s="25">
-        <x:v>46086</x:v>
+        <x:v>46037</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -876,21 +876,21 @@
         </x:is>
       </x:c>
       <x:c r="B15" t="n" s="5">
-        <x:v>2125</x:v>
+        <x:v>292.95</x:v>
       </x:c>
       <x:c r="C15" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
+          <x:t>Baker Supply, Club Member, Parts Ordered, PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D15" t="inlineStr" s="9">
         <x:is>
-          <x:t>587416074</x:t>
+          <x:t>586875916</x:t>
         </x:is>
       </x:c>
       <x:c r="E15" t="inlineStr" s="11">
         <x:is>
-          <x:t>587416074</x:t>
+          <x:t>586875916</x:t>
         </x:is>
       </x:c>
       <x:c r="F15" s="13">
@@ -898,7 +898,7 @@
       </x:c>
       <x:c r="G15" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Michael Chenoy</x:t>
+          <x:t>PP Barrington Wilson</x:t>
         </x:is>
       </x:c>
       <x:c r="H15" t="inlineStr" s="17">
@@ -908,19 +908,19 @@
       </x:c>
       <x:c r="I15" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J15" t="inlineStr" s="21">
         <x:is>
-          <x:t>Jian Jia </x:t>
+          <x:t>Anna Tyulmenkova</x:t>
         </x:is>
       </x:c>
       <x:c r="K15" s="23">
-        <x:v>46106</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="L15" s="25">
-        <x:v>46106</x:v>
+        <x:v>46100</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -934,25 +934,25 @@
       </x:c>
       <x:c r="C16" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Parts Ordered, PLM, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D16" t="inlineStr" s="9">
         <x:is>
-          <x:t>463016698</x:t>
+          <x:t>583259145</x:t>
         </x:is>
       </x:c>
       <x:c r="E16" t="inlineStr" s="11">
         <x:is>
-          <x:t>463016698</x:t>
+          <x:t>583259145</x:t>
         </x:is>
       </x:c>
       <x:c r="F16" s="13">
-        <x:v>46111</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G16" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Tyriq McCall</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="H16" t="inlineStr" s="17">
@@ -967,14 +967,14 @@
       </x:c>
       <x:c r="J16" t="inlineStr" s="21">
         <x:is>
-          <x:t>Evan Frangos</x:t>
+          <x:t>John Moore</x:t>
         </x:is>
       </x:c>
       <x:c r="K16" s="23">
-        <x:v>45762</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="L16" s="25">
-        <x:v>45762</x:v>
+        <x:v>46070</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -984,29 +984,29 @@
         </x:is>
       </x:c>
       <x:c r="B17" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>2405.92</x:v>
       </x:c>
       <x:c r="C17" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
+          <x:t>Baker Supply, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D17" t="inlineStr" s="9">
         <x:is>
-          <x:t>554749130</x:t>
+          <x:t>578394047</x:t>
         </x:is>
       </x:c>
       <x:c r="E17" t="inlineStr" s="11">
         <x:is>
-          <x:t>554749130</x:t>
+          <x:t>578394047</x:t>
         </x:is>
       </x:c>
       <x:c r="F17" s="13">
-        <x:v>46112</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G17" t="inlineStr" s="15">
         <x:is>
-          <x:t>Noel Richardson</x:t>
+          <x:t>PP Gurpreet Parihar</x:t>
         </x:is>
       </x:c>
       <x:c r="H17" t="inlineStr" s="17">
@@ -1016,19 +1016,19 @@
       </x:c>
       <x:c r="I17" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J17" t="inlineStr" s="21">
         <x:is>
-          <x:t>Mildred Rousseau</x:t>
+          <x:t>Edgar Irving</x:t>
         </x:is>
       </x:c>
       <x:c r="K17" s="23">
-        <x:v>45999</x:v>
+        <x:v>46036</x:v>
       </x:c>
       <x:c r="L17" s="25">
-        <x:v>45999</x:v>
+        <x:v>46036</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1042,25 +1042,25 @@
       </x:c>
       <x:c r="C18" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Club Member 4 sys, Parts Ordered</x:t>
+          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Club Member, Goodman distribution , Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D18" t="inlineStr" s="9">
         <x:is>
-          <x:t>586668443</x:t>
+          <x:t>585388429</x:t>
         </x:is>
       </x:c>
       <x:c r="E18" t="inlineStr" s="11">
         <x:is>
-          <x:t>586668443</x:t>
+          <x:t>585388429</x:t>
         </x:is>
       </x:c>
       <x:c r="F18" s="13">
-        <x:v>46112</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G18" t="inlineStr" s="15">
         <x:is>
-          <x:t>Bruce Coe</x:t>
+          <x:t>Rickey McClam </x:t>
         </x:is>
       </x:c>
       <x:c r="H18" t="inlineStr" s="17">
@@ -1075,14 +1075,14 @@
       </x:c>
       <x:c r="J18" t="inlineStr" s="21">
         <x:is>
-          <x:t>Harry Leiby</x:t>
+          <x:t>Charles Funkey</x:t>
         </x:is>
       </x:c>
       <x:c r="K18" s="23">
-        <x:v>46098</x:v>
+        <x:v>46086</x:v>
       </x:c>
       <x:c r="L18" s="25">
-        <x:v>46098</x:v>
+        <x:v>46086</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1092,29 +1092,29 @@
         </x:is>
       </x:c>
       <x:c r="B19" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>2125</x:v>
       </x:c>
       <x:c r="C19" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D19" t="inlineStr" s="9">
         <x:is>
-          <x:t>478958137</x:t>
+          <x:t>587416074</x:t>
         </x:is>
       </x:c>
       <x:c r="E19" t="inlineStr" s="11">
         <x:is>
-          <x:t>478958137</x:t>
+          <x:t>587416074</x:t>
         </x:is>
       </x:c>
       <x:c r="F19" s="13">
-        <x:v>46113</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G19" t="inlineStr" s="15">
         <x:is>
-          <x:t>Ezekiel Mejia-Garcia</x:t>
+          <x:t>PP Michael Chenoy</x:t>
         </x:is>
       </x:c>
       <x:c r="H19" t="inlineStr" s="17">
@@ -1124,16 +1124,16 @@
       </x:c>
       <x:c r="I19" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J19" t="inlineStr" s="21">
         <x:is>
-          <x:t>Sergio Bonadona</x:t>
+          <x:t>Jian Jia </x:t>
         </x:is>
       </x:c>
       <x:c r="K19" s="23">
-        <x:v>45864</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L19" s="25">
         <x:v>46106</x:v>
@@ -1146,100 +1146,370 @@
         </x:is>
       </x:c>
       <x:c r="B20" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C20" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D20" t="inlineStr" s="9">
+        <x:is>
+          <x:t>463016698</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E20" t="inlineStr" s="11">
+        <x:is>
+          <x:t>463016698</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F20" s="13">
+        <x:v>46111</x:v>
+      </x:c>
+      <x:c r="G20" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Tyriq McCall</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H20" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I20" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J20" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Evan Frangos</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K20" s="23">
+        <x:v>45762</x:v>
+      </x:c>
+      <x:c r="L20" s="25">
+        <x:v>45762</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B21" t="n" s="5">
+        <x:v>303.45</x:v>
+      </x:c>
+      <x:c r="C21" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D21" t="inlineStr" s="9">
+        <x:is>
+          <x:t>581332764</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E21" t="inlineStr" s="11">
+        <x:is>
+          <x:t>581332764</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F21" s="13">
+        <x:v>46111</x:v>
+      </x:c>
+      <x:c r="G21" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Justin Greene</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H21" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I21" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J21" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Chris Orsini</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K21" s="23">
+        <x:v>46057</x:v>
+      </x:c>
+      <x:c r="L21" s="25">
+        <x:v>46057</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B22" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C22" t="inlineStr" s="7">
+        <x:is>
+          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D22" t="inlineStr" s="9">
+        <x:is>
+          <x:t>554749130</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E22" t="inlineStr" s="11">
+        <x:is>
+          <x:t>554749130</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F22" s="13">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="G22" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Noel Richardson</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H22" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I22" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J22" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Mildred Rousseau</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K22" s="23">
+        <x:v>45999</x:v>
+      </x:c>
+      <x:c r="L22" s="25">
+        <x:v>45999</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B23" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C23" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Carrier enterprise, Club Member, Club Member 4 sys, Parts Ordered</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D23" t="inlineStr" s="9">
+        <x:is>
+          <x:t>586668443</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E23" t="inlineStr" s="11">
+        <x:is>
+          <x:t>586668443</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F23" s="13">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="G23" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Bruce Coe</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H23" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I23" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J23" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Harry Leiby</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K23" s="23">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="L23" s="25">
+        <x:v>46098</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B24" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C24" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D24" t="inlineStr" s="9">
+        <x:is>
+          <x:t>478958137</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E24" t="inlineStr" s="11">
+        <x:is>
+          <x:t>478958137</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F24" s="13">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="G24" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Ezekiel Mejia-Garcia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H24" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I24" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J24" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Sergio Bonadona</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K24" s="23">
+        <x:v>45864</x:v>
+      </x:c>
+      <x:c r="L24" s="25">
+        <x:v>46106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B25" t="n" s="5">
         <x:v>1167.95</x:v>
       </x:c>
-      <x:c r="C20" t="inlineStr" s="7">
+      <x:c r="C25" t="inlineStr" s="7">
         <x:is>
           <x:t>Carrier enterprise, Club Member 3 sys, Parts Ordered</x:t>
         </x:is>
       </x:c>
-      <x:c r="D20" t="inlineStr" s="9">
+      <x:c r="D25" t="inlineStr" s="9">
         <x:is>
           <x:t>587208106</x:t>
         </x:is>
       </x:c>
-      <x:c r="E20" t="inlineStr" s="11">
+      <x:c r="E25" t="inlineStr" s="11">
         <x:is>
           <x:t>587208106</x:t>
         </x:is>
       </x:c>
-      <x:c r="F20" s="13">
+      <x:c r="F25" s="13">
         <x:v>46115</x:v>
       </x:c>
-      <x:c r="G20" t="inlineStr" s="15">
+      <x:c r="G25" t="inlineStr" s="15">
         <x:is>
           <x:t>Michael Kertesz </x:t>
         </x:is>
       </x:c>
-      <x:c r="H20" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I20" t="inlineStr" s="19">
+      <x:c r="H25" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I25" t="inlineStr" s="19">
         <x:is>
           <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
-      <x:c r="J20" t="inlineStr" s="21">
+      <x:c r="J25" t="inlineStr" s="21">
         <x:is>
           <x:t>Brett Frankel</x:t>
         </x:is>
       </x:c>
-      <x:c r="K20" s="23">
+      <x:c r="K25" s="23">
         <x:v>46104</x:v>
       </x:c>
-      <x:c r="L20" s="25">
+      <x:c r="L25" s="25">
         <x:v>46104</x:v>
       </x:c>
     </x:row>
-    <x:row r="21">
-      <x:c r="A21" t="n" s="4">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B21" t="n" s="6">
-        <x:v>720.04894736842105263157894737</x:v>
-      </x:c>
-      <x:c r="C21" t="inlineStr" s="8">
+    <x:row r="26">
+      <x:c r="A26" t="n" s="4">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B26" t="n" s="6">
+        <x:v>594.88875</x:v>
+      </x:c>
+      <x:c r="C26" t="inlineStr" s="8">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D21" t="n" s="10">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E21" t="inlineStr" s="12">
+      <x:c r="D26" t="n" s="10">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E26" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F21" s="14">
+      <x:c r="F26" s="14">
         <x:v/>
       </x:c>
-      <x:c r="G21" t="inlineStr" s="16">
+      <x:c r="G26" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H21" t="inlineStr" s="18">
+      <x:c r="H26" t="inlineStr" s="18">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="I21" t="inlineStr" s="20">
+      <x:c r="I26" t="inlineStr" s="20">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="J21" t="inlineStr" s="22">
+      <x:c r="J26" t="inlineStr" s="22">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="K21" s="24">
+      <x:c r="K26" s="24">
         <x:v/>
       </x:c>
-      <x:c r="L21" s="26">
+      <x:c r="L26" s="26">
         <x:v/>
       </x:c>
     </x:row>

--- a/data/parts_report_future.xlsx
+++ b/data/parts_report_future.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R24a6892935784ec7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="R64927772b50f4963"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rea4ed7e4ad254286"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rc8e4b093214c4fbe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,29 +174,29 @@
         </x:is>
       </x:c>
       <x:c r="B2" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>289.85</x:v>
       </x:c>
       <x:c r="C2" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Received </x:t>
+          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D2" t="inlineStr" s="9">
         <x:is>
-          <x:t>586083412</x:t>
+          <x:t>587426826</x:t>
         </x:is>
       </x:c>
       <x:c r="E2" t="inlineStr" s="11">
         <x:is>
-          <x:t>586083412</x:t>
+          <x:t>587426826</x:t>
         </x:is>
       </x:c>
       <x:c r="F2" s="13">
-        <x:v>46107</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G2" t="inlineStr" s="15">
         <x:is>
-          <x:t>Michael Kertesz </x:t>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H2" t="inlineStr" s="17">
@@ -211,14 +211,14 @@
       </x:c>
       <x:c r="J2" t="inlineStr" s="21">
         <x:is>
-          <x:t>Gregory  Tsesler</x:t>
+          <x:t>Bill Esposito</x:t>
         </x:is>
       </x:c>
       <x:c r="K2" s="23">
-        <x:v>46093</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L2" s="25">
-        <x:v>46093</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -232,25 +232,25 @@
       </x:c>
       <x:c r="C3" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, Club Member, Parts Ordered, Trane Supply</x:t>
+          <x:t>Carrier enterprise, Club Member, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D3" t="inlineStr" s="9">
         <x:is>
-          <x:t>586864800</x:t>
+          <x:t>583339941</x:t>
         </x:is>
       </x:c>
       <x:c r="E3" t="inlineStr" s="11">
         <x:is>
-          <x:t>586864800</x:t>
+          <x:t>583339941</x:t>
         </x:is>
       </x:c>
       <x:c r="F3" s="13">
-        <x:v>46107</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G3" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP David Escobar</x:t>
+          <x:t>Rickey McClam </x:t>
         </x:is>
       </x:c>
       <x:c r="H3" t="inlineStr" s="17">
@@ -265,14 +265,14 @@
       </x:c>
       <x:c r="J3" t="inlineStr" s="21">
         <x:is>
-          <x:t>Hope Gadea</x:t>
+          <x:t>Walter Lizarbe</x:t>
         </x:is>
       </x:c>
       <x:c r="K3" s="23">
-        <x:v>46100</x:v>
+        <x:v>46071</x:v>
       </x:c>
       <x:c r="L3" s="25">
-        <x:v>46100</x:v>
+        <x:v>46083</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -282,29 +282,29 @@
         </x:is>
       </x:c>
       <x:c r="B4" t="n" s="5">
-        <x:v>294.96</x:v>
+        <x:v>1248.8</x:v>
       </x:c>
       <x:c r="C4" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, Club Member, Club Member (Additional System), MULTI- 2, Parts Ordered, Trane Supply</x:t>
+          <x:t>Club Member, Lennox Supply, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" t="inlineStr" s="9">
         <x:is>
-          <x:t>554624809</x:t>
+          <x:t>587303898</x:t>
         </x:is>
       </x:c>
       <x:c r="E4" t="inlineStr" s="11">
         <x:is>
-          <x:t>554624809</x:t>
+          <x:t>587303898</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" s="13">
-        <x:v>46107</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G4" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Carlos Machado</x:t>
+          <x:t>Xavier Mateo</x:t>
         </x:is>
       </x:c>
       <x:c r="H4" t="inlineStr" s="17">
@@ -319,14 +319,14 @@
       </x:c>
       <x:c r="J4" t="inlineStr" s="21">
         <x:is>
-          <x:t>Michael &amp; Delle Lenzen</x:t>
+          <x:t>ROBERT MCCABE</x:t>
         </x:is>
       </x:c>
       <x:c r="K4" s="23">
-        <x:v>45996</x:v>
+        <x:v>46105</x:v>
       </x:c>
       <x:c r="L4" s="25">
-        <x:v>45996</x:v>
+        <x:v>46105</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -336,29 +336,29 @@
         </x:is>
       </x:c>
       <x:c r="B5" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1267.95</x:v>
       </x:c>
       <x:c r="C5" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, LW- 2 YEAR LABOR, Parts Ordered, Trane Supply</x:t>
+          <x:t>Club Member 3 sys, Gemaire, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D5" t="inlineStr" s="9">
         <x:is>
-          <x:t>587077196</x:t>
+          <x:t>578585007</x:t>
         </x:is>
       </x:c>
       <x:c r="E5" t="inlineStr" s="11">
         <x:is>
-          <x:t>587077196</x:t>
+          <x:t>578585007</x:t>
         </x:is>
       </x:c>
       <x:c r="F5" s="13">
-        <x:v>46107</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G5" t="inlineStr" s="15">
         <x:is>
-          <x:t>Tyler Gallatin</x:t>
+          <x:t>PP Cesar Levy</x:t>
         </x:is>
       </x:c>
       <x:c r="H5" t="inlineStr" s="17">
@@ -373,14 +373,14 @@
       </x:c>
       <x:c r="J5" t="inlineStr" s="21">
         <x:is>
-          <x:t>Timberwalk Association Inc</x:t>
+          <x:t>Serghei Arsentiev</x:t>
         </x:is>
       </x:c>
       <x:c r="K5" s="23">
-        <x:v>46102</x:v>
+        <x:v>46037</x:v>
       </x:c>
       <x:c r="L5" s="25">
-        <x:v>46102</x:v>
+        <x:v>46037</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -390,29 +390,29 @@
         </x:is>
       </x:c>
       <x:c r="B6" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>292.95</x:v>
       </x:c>
       <x:c r="C6" t="inlineStr" s="7">
         <x:is>
-          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member 3 sys, Gemaire, MULTI- 3, Parts Ordered</x:t>
+          <x:t>Baker Supply, Club Member, Parts Ordered, PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D6" t="inlineStr" s="9">
         <x:is>
-          <x:t>586595677</x:t>
+          <x:t>586875916</x:t>
         </x:is>
       </x:c>
       <x:c r="E6" t="inlineStr" s="11">
         <x:is>
-          <x:t>586595677</x:t>
+          <x:t>586875916</x:t>
         </x:is>
       </x:c>
       <x:c r="F6" s="13">
-        <x:v>46107</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G6" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
+          <x:t>PP Barrington Wilson</x:t>
         </x:is>
       </x:c>
       <x:c r="H6" t="inlineStr" s="17">
@@ -422,19 +422,19 @@
       </x:c>
       <x:c r="I6" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J6" t="inlineStr" s="21">
         <x:is>
-          <x:t>Bob Lauson</x:t>
+          <x:t>Anna Tyulmenkova</x:t>
         </x:is>
       </x:c>
       <x:c r="K6" s="23">
-        <x:v>46098</x:v>
+        <x:v>46100</x:v>
       </x:c>
       <x:c r="L6" s="25">
-        <x:v>46098</x:v>
+        <x:v>46100</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -448,25 +448,25 @@
       </x:c>
       <x:c r="C7" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Goodman distribution , MULTI- 5, Parts Ordered, PLM, Potential Member</x:t>
+          <x:t>Carrier enterprise, Parts Ordered, PLM, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D7" t="inlineStr" s="9">
         <x:is>
-          <x:t>587266021</x:t>
+          <x:t>583259145</x:t>
         </x:is>
       </x:c>
       <x:c r="E7" t="inlineStr" s="11">
         <x:is>
-          <x:t>587266021</x:t>
+          <x:t>583259145</x:t>
         </x:is>
       </x:c>
       <x:c r="F7" s="13">
-        <x:v>46107</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G7" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Cesar Levy</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="H7" t="inlineStr" s="17">
@@ -476,19 +476,19 @@
       </x:c>
       <x:c r="I7" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J7" t="inlineStr" s="21">
         <x:is>
-          <x:t>Nevalee &amp; Paul Oneil</x:t>
+          <x:t>John Moore</x:t>
         </x:is>
       </x:c>
       <x:c r="K7" s="23">
-        <x:v>46105</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="L7" s="25">
-        <x:v>46105</x:v>
+        <x:v>46070</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -498,29 +498,29 @@
         </x:is>
       </x:c>
       <x:c r="B8" t="n" s="5">
-        <x:v>1340.1</x:v>
+        <x:v>2405.92</x:v>
       </x:c>
       <x:c r="C8" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Club Member (Additional System), Gemaire, MULTI- 3, Parts Received , PLM</x:t>
+          <x:t>Baker Supply, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D8" t="inlineStr" s="9">
         <x:is>
-          <x:t>587281524</x:t>
+          <x:t>578394047</x:t>
         </x:is>
       </x:c>
       <x:c r="E8" t="inlineStr" s="11">
         <x:is>
-          <x:t>587281524</x:t>
+          <x:t>578394047</x:t>
         </x:is>
       </x:c>
       <x:c r="F8" s="13">
-        <x:v>46107</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G8" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
+          <x:t>PP Gurpreet Parihar</x:t>
         </x:is>
       </x:c>
       <x:c r="H8" t="inlineStr" s="17">
@@ -535,14 +535,14 @@
       </x:c>
       <x:c r="J8" t="inlineStr" s="21">
         <x:is>
-          <x:t>Robert Lake</x:t>
+          <x:t>Edgar Irving</x:t>
         </x:is>
       </x:c>
       <x:c r="K8" s="23">
-        <x:v>46105</x:v>
+        <x:v>46036</x:v>
       </x:c>
       <x:c r="L8" s="25">
-        <x:v>46105</x:v>
+        <x:v>46036</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -552,29 +552,29 @@
         </x:is>
       </x:c>
       <x:c r="B9" t="n" s="5">
-        <x:v>3247.45</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C9" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, Club Member, Club Member 2 sys , Gemaire, Parts Received , PLM</x:t>
+          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Club Member, Goodman distribution , Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D9" t="inlineStr" s="9">
         <x:is>
-          <x:t>587314216</x:t>
+          <x:t>585388429</x:t>
         </x:is>
       </x:c>
       <x:c r="E9" t="inlineStr" s="11">
         <x:is>
-          <x:t>587314216</x:t>
+          <x:t>585388429</x:t>
         </x:is>
       </x:c>
       <x:c r="F9" s="13">
-        <x:v>46107</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G9" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t>Rickey McClam </x:t>
         </x:is>
       </x:c>
       <x:c r="H9" t="inlineStr" s="17">
@@ -589,14 +589,14 @@
       </x:c>
       <x:c r="J9" t="inlineStr" s="21">
         <x:is>
-          <x:t>FRIEDMAN, SAMANTHA</x:t>
+          <x:t>Charles Funkey</x:t>
         </x:is>
       </x:c>
       <x:c r="K9" s="23">
-        <x:v>46105</x:v>
+        <x:v>46086</x:v>
       </x:c>
       <x:c r="L9" s="25">
-        <x:v>46105</x:v>
+        <x:v>46086</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -606,29 +606,29 @@
         </x:is>
       </x:c>
       <x:c r="B10" t="n" s="5">
-        <x:v>292.95</x:v>
+        <x:v>2125</x:v>
       </x:c>
       <x:c r="C10" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Club Member, Parts Ordered, PLM</x:t>
+          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D10" t="inlineStr" s="9">
         <x:is>
-          <x:t>587301961</x:t>
+          <x:t>587416074</x:t>
         </x:is>
       </x:c>
       <x:c r="E10" t="inlineStr" s="11">
         <x:is>
-          <x:t>587301961</x:t>
+          <x:t>587416074</x:t>
         </x:is>
       </x:c>
       <x:c r="F10" s="13">
-        <x:v>46107</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="G10" t="inlineStr" s="15">
         <x:is>
-          <x:t>Jesse Dague</x:t>
+          <x:t>PP Michael Chenoy</x:t>
         </x:is>
       </x:c>
       <x:c r="H10" t="inlineStr" s="17">
@@ -638,19 +638,19 @@
       </x:c>
       <x:c r="I10" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J10" t="inlineStr" s="21">
         <x:is>
-          <x:t>CHACON, LERA</x:t>
+          <x:t>Jian Jia </x:t>
         </x:is>
       </x:c>
       <x:c r="K10" s="23">
-        <x:v>46105</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L10" s="25">
-        <x:v>46105</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -660,29 +660,29 @@
         </x:is>
       </x:c>
       <x:c r="B11" t="n" s="5">
-        <x:v>289.85</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C11" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
+          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D11" t="inlineStr" s="9">
         <x:is>
-          <x:t>587426826</x:t>
+          <x:t>463016698</x:t>
         </x:is>
       </x:c>
       <x:c r="E11" t="inlineStr" s="11">
         <x:is>
-          <x:t>587426826</x:t>
+          <x:t>463016698</x:t>
         </x:is>
       </x:c>
       <x:c r="F11" s="13">
-        <x:v>46108</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G11" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t>PP Tyriq McCall</x:t>
         </x:is>
       </x:c>
       <x:c r="H11" t="inlineStr" s="17">
@@ -697,14 +697,14 @@
       </x:c>
       <x:c r="J11" t="inlineStr" s="21">
         <x:is>
-          <x:t>Bill Esposito</x:t>
+          <x:t>Evan Frangos</x:t>
         </x:is>
       </x:c>
       <x:c r="K11" s="23">
-        <x:v>46106</x:v>
+        <x:v>45762</x:v>
       </x:c>
       <x:c r="L11" s="25">
-        <x:v>46106</x:v>
+        <x:v>45762</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -714,29 +714,29 @@
         </x:is>
       </x:c>
       <x:c r="B12" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>303.45</x:v>
       </x:c>
       <x:c r="C12" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Received </x:t>
+          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D12" t="inlineStr" s="9">
         <x:is>
-          <x:t>583339941</x:t>
+          <x:t>581332764</x:t>
         </x:is>
       </x:c>
       <x:c r="E12" t="inlineStr" s="11">
         <x:is>
-          <x:t>583339941</x:t>
+          <x:t>581332764</x:t>
         </x:is>
       </x:c>
       <x:c r="F12" s="13">
-        <x:v>46108</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G12" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rickey McClam </x:t>
+          <x:t>Justin Greene</x:t>
         </x:is>
       </x:c>
       <x:c r="H12" t="inlineStr" s="17">
@@ -751,14 +751,14 @@
       </x:c>
       <x:c r="J12" t="inlineStr" s="21">
         <x:is>
-          <x:t>Walter Lizarbe</x:t>
+          <x:t>Chris Orsini</x:t>
         </x:is>
       </x:c>
       <x:c r="K12" s="23">
-        <x:v>46071</x:v>
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L12" s="25">
-        <x:v>46083</x:v>
+        <x:v>46057</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -768,29 +768,29 @@
         </x:is>
       </x:c>
       <x:c r="B13" t="n" s="5">
-        <x:v>1248.8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C13" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Lennox Supply, Parts Ordered</x:t>
+          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D13" t="inlineStr" s="9">
         <x:is>
-          <x:t>587303898</x:t>
+          <x:t>554749130</x:t>
         </x:is>
       </x:c>
       <x:c r="E13" t="inlineStr" s="11">
         <x:is>
-          <x:t>587303898</x:t>
+          <x:t>554749130</x:t>
         </x:is>
       </x:c>
       <x:c r="F13" s="13">
-        <x:v>46108</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="G13" t="inlineStr" s="15">
         <x:is>
-          <x:t>Xavier Mateo</x:t>
+          <x:t>Noel Richardson</x:t>
         </x:is>
       </x:c>
       <x:c r="H13" t="inlineStr" s="17">
@@ -805,14 +805,14 @@
       </x:c>
       <x:c r="J13" t="inlineStr" s="21">
         <x:is>
-          <x:t>ROBERT MCCABE</x:t>
+          <x:t>Mildred Rousseau</x:t>
         </x:is>
       </x:c>
       <x:c r="K13" s="23">
-        <x:v>46105</x:v>
+        <x:v>45999</x:v>
       </x:c>
       <x:c r="L13" s="25">
-        <x:v>46105</x:v>
+        <x:v>45999</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -822,29 +822,29 @@
         </x:is>
       </x:c>
       <x:c r="B14" t="n" s="5">
-        <x:v>1267.95</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C14" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member 3 sys, Gemaire, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Club Member, Club Member 4 sys, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D14" t="inlineStr" s="9">
         <x:is>
-          <x:t>578585007</x:t>
+          <x:t>586668443</x:t>
         </x:is>
       </x:c>
       <x:c r="E14" t="inlineStr" s="11">
         <x:is>
-          <x:t>578585007</x:t>
+          <x:t>586668443</x:t>
         </x:is>
       </x:c>
       <x:c r="F14" s="13">
-        <x:v>46108</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="G14" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Cesar Levy</x:t>
+          <x:t>Bruce Coe</x:t>
         </x:is>
       </x:c>
       <x:c r="H14" t="inlineStr" s="17">
@@ -859,14 +859,14 @@
       </x:c>
       <x:c r="J14" t="inlineStr" s="21">
         <x:is>
-          <x:t>Serghei Arsentiev</x:t>
+          <x:t>Harry Leiby</x:t>
         </x:is>
       </x:c>
       <x:c r="K14" s="23">
-        <x:v>46037</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="L14" s="25">
-        <x:v>46037</x:v>
+        <x:v>46098</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -876,29 +876,29 @@
         </x:is>
       </x:c>
       <x:c r="B15" t="n" s="5">
-        <x:v>292.95</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C15" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Club Member, Parts Ordered, PLM</x:t>
+          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D15" t="inlineStr" s="9">
         <x:is>
-          <x:t>586875916</x:t>
+          <x:t>478958137</x:t>
         </x:is>
       </x:c>
       <x:c r="E15" t="inlineStr" s="11">
         <x:is>
-          <x:t>586875916</x:t>
+          <x:t>478958137</x:t>
         </x:is>
       </x:c>
       <x:c r="F15" s="13">
-        <x:v>46108</x:v>
+        <x:v>46113</x:v>
       </x:c>
       <x:c r="G15" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Barrington Wilson</x:t>
+          <x:t>Ezekiel Mejia-Garcia</x:t>
         </x:is>
       </x:c>
       <x:c r="H15" t="inlineStr" s="17">
@@ -913,14 +913,14 @@
       </x:c>
       <x:c r="J15" t="inlineStr" s="21">
         <x:is>
-          <x:t>Anna Tyulmenkova</x:t>
+          <x:t>Sergio Bonadona</x:t>
         </x:is>
       </x:c>
       <x:c r="K15" s="23">
-        <x:v>46100</x:v>
+        <x:v>45864</x:v>
       </x:c>
       <x:c r="L15" s="25">
-        <x:v>46100</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -930,586 +930,100 @@
         </x:is>
       </x:c>
       <x:c r="B16" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1167.95</x:v>
       </x:c>
       <x:c r="C16" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, PLM, Potential Member</x:t>
+          <x:t>Carrier enterprise, Club Member 3 sys, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D16" t="inlineStr" s="9">
         <x:is>
-          <x:t>583259145</x:t>
+          <x:t>587208106</x:t>
         </x:is>
       </x:c>
       <x:c r="E16" t="inlineStr" s="11">
         <x:is>
-          <x:t>583259145</x:t>
+          <x:t>587208106</x:t>
         </x:is>
       </x:c>
       <x:c r="F16" s="13">
-        <x:v>46108</x:v>
+        <x:v>46115</x:v>
       </x:c>
       <x:c r="G16" t="inlineStr" s="15">
         <x:is>
+          <x:t>Michael Kertesz </x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H16" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I16" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J16" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Brett Frankel</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K16" s="23">
+        <x:v>46104</x:v>
+      </x:c>
+      <x:c r="L16" s="25">
+        <x:v>46104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="n" s="4">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B17" t="n" s="6">
+        <x:v>606.79133333333333333333333333</x:v>
+      </x:c>
+      <x:c r="C17" t="inlineStr" s="8">
+        <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H16" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I16" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J16" t="inlineStr" s="21">
-        <x:is>
-          <x:t>John Moore</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K16" s="23">
-        <x:v>46070</x:v>
-      </x:c>
-      <x:c r="L16" s="25">
-        <x:v>46070</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B17" t="n" s="5">
-        <x:v>2405.92</x:v>
-      </x:c>
-      <x:c r="C17" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Baker Supply, Parts Ordered, Potential Member</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D17" t="inlineStr" s="9">
-        <x:is>
-          <x:t>578394047</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E17" t="inlineStr" s="11">
-        <x:is>
-          <x:t>578394047</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F17" s="13">
-        <x:v>46108</x:v>
-      </x:c>
-      <x:c r="G17" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Gurpreet Parihar</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H17" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I17" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J17" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Edgar Irving</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K17" s="23">
-        <x:v>46036</x:v>
-      </x:c>
-      <x:c r="L17" s="25">
-        <x:v>46036</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B18" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C18" t="inlineStr" s="7">
-        <x:is>
-          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Club Member, Goodman distribution , Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D18" t="inlineStr" s="9">
-        <x:is>
-          <x:t>585388429</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E18" t="inlineStr" s="11">
-        <x:is>
-          <x:t>585388429</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F18" s="13">
-        <x:v>46108</x:v>
-      </x:c>
-      <x:c r="G18" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Rickey McClam </x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H18" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I18" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J18" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Charles Funkey</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K18" s="23">
-        <x:v>46086</x:v>
-      </x:c>
-      <x:c r="L18" s="25">
-        <x:v>46086</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B19" t="n" s="5">
-        <x:v>2125</x:v>
-      </x:c>
-      <x:c r="C19" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D19" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587416074</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E19" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587416074</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F19" s="13">
-        <x:v>46108</x:v>
-      </x:c>
-      <x:c r="G19" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Michael Chenoy</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H19" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I19" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J19" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Jian Jia </x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K19" s="23">
-        <x:v>46106</x:v>
-      </x:c>
-      <x:c r="L19" s="25">
-        <x:v>46106</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B20" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C20" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D20" t="inlineStr" s="9">
-        <x:is>
-          <x:t>463016698</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E20" t="inlineStr" s="11">
-        <x:is>
-          <x:t>463016698</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F20" s="13">
-        <x:v>46111</x:v>
-      </x:c>
-      <x:c r="G20" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Tyriq McCall</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H20" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I20" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J20" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Evan Frangos</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K20" s="23">
-        <x:v>45762</x:v>
-      </x:c>
-      <x:c r="L20" s="25">
-        <x:v>45762</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B21" t="n" s="5">
-        <x:v>303.45</x:v>
-      </x:c>
-      <x:c r="C21" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D21" t="inlineStr" s="9">
-        <x:is>
-          <x:t>581332764</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E21" t="inlineStr" s="11">
-        <x:is>
-          <x:t>581332764</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F21" s="13">
-        <x:v>46111</x:v>
-      </x:c>
-      <x:c r="G21" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Justin Greene</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H21" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I21" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J21" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Chris Orsini</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K21" s="23">
-        <x:v>46057</x:v>
-      </x:c>
-      <x:c r="L21" s="25">
-        <x:v>46057</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B22" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C22" t="inlineStr" s="7">
-        <x:is>
-          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D22" t="inlineStr" s="9">
-        <x:is>
-          <x:t>554749130</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E22" t="inlineStr" s="11">
-        <x:is>
-          <x:t>554749130</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F22" s="13">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="G22" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Noel Richardson</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H22" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I22" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J22" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Mildred Rousseau</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K22" s="23">
-        <x:v>45999</x:v>
-      </x:c>
-      <x:c r="L22" s="25">
-        <x:v>45999</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B23" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C23" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Club Member, Club Member 4 sys, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D23" t="inlineStr" s="9">
-        <x:is>
-          <x:t>586668443</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E23" t="inlineStr" s="11">
-        <x:is>
-          <x:t>586668443</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F23" s="13">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="G23" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Bruce Coe</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H23" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I23" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J23" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Harry Leiby</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K23" s="23">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="L23" s="25">
-        <x:v>46098</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B24" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C24" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D24" t="inlineStr" s="9">
-        <x:is>
-          <x:t>478958137</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E24" t="inlineStr" s="11">
-        <x:is>
-          <x:t>478958137</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F24" s="13">
-        <x:v>46113</x:v>
-      </x:c>
-      <x:c r="G24" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Ezekiel Mejia-Garcia</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H24" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I24" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J24" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Sergio Bonadona</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K24" s="23">
-        <x:v>45864</x:v>
-      </x:c>
-      <x:c r="L24" s="25">
-        <x:v>46106</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B25" t="n" s="5">
-        <x:v>1167.95</x:v>
-      </x:c>
-      <x:c r="C25" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Club Member 3 sys, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D25" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587208106</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E25" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587208106</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F25" s="13">
-        <x:v>46115</x:v>
-      </x:c>
-      <x:c r="G25" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Michael Kertesz </x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H25" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I25" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J25" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Brett Frankel</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K25" s="23">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="L25" s="25">
-        <x:v>46104</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" t="n" s="4">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B26" t="n" s="6">
-        <x:v>594.88875</x:v>
-      </x:c>
-      <x:c r="C26" t="inlineStr" s="8">
+      <x:c r="D17" t="n" s="10">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E17" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D26" t="n" s="10">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E26" t="inlineStr" s="12">
+      <x:c r="F17" s="14">
+        <x:v/>
+      </x:c>
+      <x:c r="G17" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F26" s="14">
+      <x:c r="H17" t="inlineStr" s="18">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="I17" t="inlineStr" s="20">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="J17" t="inlineStr" s="22">
+        <x:is>
+          <x:t/>
+        </x:is>
+      </x:c>
+      <x:c r="K17" s="24">
         <x:v/>
       </x:c>
-      <x:c r="G26" t="inlineStr" s="16">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="H26" t="inlineStr" s="18">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="I26" t="inlineStr" s="20">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="J26" t="inlineStr" s="22">
-        <x:is>
-          <x:t/>
-        </x:is>
-      </x:c>
-      <x:c r="K26" s="24">
-        <x:v/>
-      </x:c>
-      <x:c r="L26" s="26">
+      <x:c r="L17" s="26">
         <x:v/>
       </x:c>
     </x:row>
@@ -1540,7 +1054,7 @@
       </x:c>
       <x:c r="B2" t="inlineStr" s="28">
         <x:is>
-          <x:t>03/26/26 - 03/25/27</x:t>
+          <x:t>03/27/26 - 03/26/27</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1606,7 +1120,7 @@
     <x:mergeCell ref="A8:B8"/>
   </x:mergeCells>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="hyperlinkId1" location="/new/reports/459565681?DateType=3&amp;BusinessUnitId=2415185%2C2415187%2C15775258%2C2415186%2C2415190%2C182981963%2C182981958%2C182981961%2C182981957&amp;IncludeAdjustmentInvoices=false&amp;IsScheduling=True&amp;From=2026-03-26&amp;To=2027-03-25" display="View Report"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="hyperlinkId1" location="/new/reports/459565681?DateType=3&amp;BusinessUnitId=2415185%2C2415187%2C15775258%2C2415186%2C2415190%2C182981963%2C182981958%2C182981961%2C182981957&amp;IncludeAdjustmentInvoices=false&amp;IsScheduling=True&amp;From=2026-03-27&amp;To=2027-03-26" display="View Report"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/data/parts_report_future.xlsx
+++ b/data/parts_report_future.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rea4ed7e4ad254286"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rc8e4b093214c4fbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf19309e97e804340"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rb5b1f8ba08c843f0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,21 +174,21 @@
         </x:is>
       </x:c>
       <x:c r="B2" t="n" s="5">
-        <x:v>289.85</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C2" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
+          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D2" t="inlineStr" s="9">
         <x:is>
-          <x:t>587426826</x:t>
+          <x:t>587448096</x:t>
         </x:is>
       </x:c>
       <x:c r="E2" t="inlineStr" s="11">
         <x:is>
-          <x:t>587426826</x:t>
+          <x:t>587448096</x:t>
         </x:is>
       </x:c>
       <x:c r="F2" s="13">
@@ -196,7 +196,7 @@
       </x:c>
       <x:c r="G2" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="H2" t="inlineStr" s="17">
@@ -206,12 +206,12 @@
       </x:c>
       <x:c r="I2" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J2" t="inlineStr" s="21">
         <x:is>
-          <x:t>Bill Esposito</x:t>
+          <x:t>Cassandra Sexton</x:t>
         </x:is>
       </x:c>
       <x:c r="K2" s="23">
@@ -228,21 +228,21 @@
         </x:is>
       </x:c>
       <x:c r="B3" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>289.85</x:v>
       </x:c>
       <x:c r="C3" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Received </x:t>
+          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D3" t="inlineStr" s="9">
         <x:is>
-          <x:t>583339941</x:t>
+          <x:t>587426826</x:t>
         </x:is>
       </x:c>
       <x:c r="E3" t="inlineStr" s="11">
         <x:is>
-          <x:t>583339941</x:t>
+          <x:t>587426826</x:t>
         </x:is>
       </x:c>
       <x:c r="F3" s="13">
@@ -250,7 +250,7 @@
       </x:c>
       <x:c r="G3" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rickey McClam </x:t>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H3" t="inlineStr" s="17">
@@ -265,14 +265,14 @@
       </x:c>
       <x:c r="J3" t="inlineStr" s="21">
         <x:is>
-          <x:t>Walter Lizarbe</x:t>
+          <x:t>Bill Esposito</x:t>
         </x:is>
       </x:c>
       <x:c r="K3" s="23">
-        <x:v>46071</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L3" s="25">
-        <x:v>46083</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -664,17 +664,17 @@
       </x:c>
       <x:c r="C11" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
+          <x:t>Club Member, Parts Ordered, Trane Supply</x:t>
         </x:is>
       </x:c>
       <x:c r="D11" t="inlineStr" s="9">
         <x:is>
-          <x:t>463016698</x:t>
+          <x:t>587375373</x:t>
         </x:is>
       </x:c>
       <x:c r="E11" t="inlineStr" s="11">
         <x:is>
-          <x:t>463016698</x:t>
+          <x:t>587375373</x:t>
         </x:is>
       </x:c>
       <x:c r="F11" s="13">
@@ -682,7 +682,7 @@
       </x:c>
       <x:c r="G11" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Tyriq McCall</x:t>
+          <x:t>PP Ryley Johnson</x:t>
         </x:is>
       </x:c>
       <x:c r="H11" t="inlineStr" s="17">
@@ -697,14 +697,14 @@
       </x:c>
       <x:c r="J11" t="inlineStr" s="21">
         <x:is>
-          <x:t>Evan Frangos</x:t>
+          <x:t>Laurie Kline</x:t>
         </x:is>
       </x:c>
       <x:c r="K11" s="23">
-        <x:v>45762</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L11" s="25">
-        <x:v>45762</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -714,21 +714,21 @@
         </x:is>
       </x:c>
       <x:c r="B12" t="n" s="5">
-        <x:v>303.45</x:v>
+        <x:v>462.83</x:v>
       </x:c>
       <x:c r="C12" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
+          <x:t>Baker Supply, Club Member, Parts Ordered, PLM, Potential Membership Renewal, Residential Maintenance Agreement</x:t>
         </x:is>
       </x:c>
       <x:c r="D12" t="inlineStr" s="9">
         <x:is>
-          <x:t>581332764</x:t>
+          <x:t>555552166</x:t>
         </x:is>
       </x:c>
       <x:c r="E12" t="inlineStr" s="11">
         <x:is>
-          <x:t>581332764</x:t>
+          <x:t>555552166</x:t>
         </x:is>
       </x:c>
       <x:c r="F12" s="13">
@@ -736,7 +736,7 @@
       </x:c>
       <x:c r="G12" t="inlineStr" s="15">
         <x:is>
-          <x:t>Justin Greene</x:t>
+          <x:t>PP Cesar Levy</x:t>
         </x:is>
       </x:c>
       <x:c r="H12" t="inlineStr" s="17">
@@ -746,19 +746,19 @@
       </x:c>
       <x:c r="I12" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J12" t="inlineStr" s="21">
         <x:is>
-          <x:t>Chris Orsini</x:t>
+          <x:t>Wanda Betancourt</x:t>
         </x:is>
       </x:c>
       <x:c r="K12" s="23">
-        <x:v>46057</x:v>
+        <x:v>46007</x:v>
       </x:c>
       <x:c r="L12" s="25">
-        <x:v>46057</x:v>
+        <x:v>46007</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -768,29 +768,29 @@
         </x:is>
       </x:c>
       <x:c r="B13" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>945.4</x:v>
       </x:c>
       <x:c r="C13" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Club Member, Parts Ordered, PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D13" t="inlineStr" s="9">
         <x:is>
-          <x:t>554749130</x:t>
+          <x:t>587403893</x:t>
         </x:is>
       </x:c>
       <x:c r="E13" t="inlineStr" s="11">
         <x:is>
-          <x:t>554749130</x:t>
+          <x:t>587403893</x:t>
         </x:is>
       </x:c>
       <x:c r="F13" s="13">
-        <x:v>46112</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G13" t="inlineStr" s="15">
         <x:is>
-          <x:t>Noel Richardson</x:t>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H13" t="inlineStr" s="17">
@@ -800,19 +800,19 @@
       </x:c>
       <x:c r="I13" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J13" t="inlineStr" s="21">
         <x:is>
-          <x:t>Mildred Rousseau</x:t>
+          <x:t>WALKER, CAMERON</x:t>
         </x:is>
       </x:c>
       <x:c r="K13" s="23">
-        <x:v>45999</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L13" s="25">
-        <x:v>45999</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -826,25 +826,25 @@
       </x:c>
       <x:c r="C14" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Club Member 4 sys, Parts Ordered</x:t>
+          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D14" t="inlineStr" s="9">
         <x:is>
-          <x:t>586668443</x:t>
+          <x:t>463016698</x:t>
         </x:is>
       </x:c>
       <x:c r="E14" t="inlineStr" s="11">
         <x:is>
-          <x:t>586668443</x:t>
+          <x:t>463016698</x:t>
         </x:is>
       </x:c>
       <x:c r="F14" s="13">
-        <x:v>46112</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G14" t="inlineStr" s="15">
         <x:is>
-          <x:t>Bruce Coe</x:t>
+          <x:t>PP Tyriq McCall</x:t>
         </x:is>
       </x:c>
       <x:c r="H14" t="inlineStr" s="17">
@@ -859,14 +859,14 @@
       </x:c>
       <x:c r="J14" t="inlineStr" s="21">
         <x:is>
-          <x:t>Harry Leiby</x:t>
+          <x:t>Evan Frangos</x:t>
         </x:is>
       </x:c>
       <x:c r="K14" s="23">
-        <x:v>46098</x:v>
+        <x:v>45762</x:v>
       </x:c>
       <x:c r="L14" s="25">
-        <x:v>46098</x:v>
+        <x:v>45762</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -876,29 +876,29 @@
         </x:is>
       </x:c>
       <x:c r="B15" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>303.45</x:v>
       </x:c>
       <x:c r="C15" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D15" t="inlineStr" s="9">
         <x:is>
-          <x:t>478958137</x:t>
+          <x:t>581332764</x:t>
         </x:is>
       </x:c>
       <x:c r="E15" t="inlineStr" s="11">
         <x:is>
-          <x:t>478958137</x:t>
+          <x:t>581332764</x:t>
         </x:is>
       </x:c>
       <x:c r="F15" s="13">
-        <x:v>46113</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G15" t="inlineStr" s="15">
         <x:is>
-          <x:t>Ezekiel Mejia-Garcia</x:t>
+          <x:t>Justin Greene</x:t>
         </x:is>
       </x:c>
       <x:c r="H15" t="inlineStr" s="17">
@@ -913,14 +913,14 @@
       </x:c>
       <x:c r="J15" t="inlineStr" s="21">
         <x:is>
-          <x:t>Sergio Bonadona</x:t>
+          <x:t>Chris Orsini</x:t>
         </x:is>
       </x:c>
       <x:c r="K15" s="23">
-        <x:v>45864</x:v>
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L15" s="25">
-        <x:v>46106</x:v>
+        <x:v>46057</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -930,100 +930,316 @@
         </x:is>
       </x:c>
       <x:c r="B16" t="n" s="5">
+        <x:v>710.85</x:v>
+      </x:c>
+      <x:c r="C16" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Gemaire, Parts Ordered, Potential Member</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D16" t="inlineStr" s="9">
+        <x:is>
+          <x:t>580795172</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E16" t="inlineStr" s="11">
+        <x:is>
+          <x:t>580795172</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F16" s="13">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="G16" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Alejandro Espinosa</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H16" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I16" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J16" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Paul Serota</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K16" s="23">
+        <x:v>46054</x:v>
+      </x:c>
+      <x:c r="L16" s="25">
+        <x:v>46054</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B17" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C17" t="inlineStr" s="7">
+        <x:is>
+          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" t="inlineStr" s="9">
+        <x:is>
+          <x:t>554749130</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E17" t="inlineStr" s="11">
+        <x:is>
+          <x:t>554749130</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F17" s="13">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="G17" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Noel Richardson</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H17" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I17" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J17" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Mildred Rousseau</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K17" s="23">
+        <x:v>45999</x:v>
+      </x:c>
+      <x:c r="L17" s="25">
+        <x:v>45999</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B18" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C18" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Carrier enterprise, Club Member, Club Member 4 sys, Parts Ordered</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D18" t="inlineStr" s="9">
+        <x:is>
+          <x:t>586668443</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E18" t="inlineStr" s="11">
+        <x:is>
+          <x:t>586668443</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F18" s="13">
+        <x:v>46112</x:v>
+      </x:c>
+      <x:c r="G18" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Bruce Coe</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H18" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I18" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J18" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Harry Leiby</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K18" s="23">
+        <x:v>46098</x:v>
+      </x:c>
+      <x:c r="L18" s="25">
+        <x:v>46098</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B19" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C19" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D19" t="inlineStr" s="9">
+        <x:is>
+          <x:t>478958137</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E19" t="inlineStr" s="11">
+        <x:is>
+          <x:t>478958137</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F19" s="13">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="G19" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Ezekiel Mejia-Garcia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H19" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I19" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J19" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Sergio Bonadona</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K19" s="23">
+        <x:v>45864</x:v>
+      </x:c>
+      <x:c r="L19" s="25">
+        <x:v>46106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B20" t="n" s="5">
         <x:v>1167.95</x:v>
       </x:c>
-      <x:c r="C16" t="inlineStr" s="7">
+      <x:c r="C20" t="inlineStr" s="7">
         <x:is>
           <x:t>Carrier enterprise, Club Member 3 sys, Parts Ordered</x:t>
         </x:is>
       </x:c>
-      <x:c r="D16" t="inlineStr" s="9">
+      <x:c r="D20" t="inlineStr" s="9">
         <x:is>
           <x:t>587208106</x:t>
         </x:is>
       </x:c>
-      <x:c r="E16" t="inlineStr" s="11">
+      <x:c r="E20" t="inlineStr" s="11">
         <x:is>
           <x:t>587208106</x:t>
         </x:is>
       </x:c>
-      <x:c r="F16" s="13">
+      <x:c r="F20" s="13">
         <x:v>46115</x:v>
       </x:c>
-      <x:c r="G16" t="inlineStr" s="15">
+      <x:c r="G20" t="inlineStr" s="15">
         <x:is>
           <x:t>Michael Kertesz </x:t>
         </x:is>
       </x:c>
-      <x:c r="H16" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I16" t="inlineStr" s="19">
+      <x:c r="H20" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I20" t="inlineStr" s="19">
         <x:is>
           <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
-      <x:c r="J16" t="inlineStr" s="21">
+      <x:c r="J20" t="inlineStr" s="21">
         <x:is>
           <x:t>Brett Frankel</x:t>
         </x:is>
       </x:c>
-      <x:c r="K16" s="23">
+      <x:c r="K20" s="23">
         <x:v>46104</x:v>
       </x:c>
-      <x:c r="L16" s="25">
+      <x:c r="L20" s="25">
         <x:v>46104</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="n" s="4">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B17" t="n" s="6">
-        <x:v>606.79133333333333333333333333</x:v>
-      </x:c>
-      <x:c r="C17" t="inlineStr" s="8">
+    <x:row r="21">
+      <x:c r="A21" t="n" s="4">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B21" t="n" s="6">
+        <x:v>590.57631578947368421052631579</x:v>
+      </x:c>
+      <x:c r="C21" t="inlineStr" s="8">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D17" t="n" s="10">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E17" t="inlineStr" s="12">
+      <x:c r="D21" t="n" s="10">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E21" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F17" s="14">
+      <x:c r="F21" s="14">
         <x:v/>
       </x:c>
-      <x:c r="G17" t="inlineStr" s="16">
+      <x:c r="G21" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H17" t="inlineStr" s="18">
+      <x:c r="H21" t="inlineStr" s="18">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="I17" t="inlineStr" s="20">
+      <x:c r="I21" t="inlineStr" s="20">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="J17" t="inlineStr" s="22">
+      <x:c r="J21" t="inlineStr" s="22">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="K17" s="24">
+      <x:c r="K21" s="24">
         <x:v/>
       </x:c>
-      <x:c r="L17" s="26">
+      <x:c r="L21" s="26">
         <x:v/>
       </x:c>
     </x:row>

--- a/data/parts_report_future.xlsx
+++ b/data/parts_report_future.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf19309e97e804340"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rb5b1f8ba08c843f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R825f89300db84672"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="R1e9f292fc257427f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -232,7 +232,7 @@
       </x:c>
       <x:c r="C3" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
+          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Received </x:t>
         </x:is>
       </x:c>
       <x:c r="D3" t="inlineStr" s="9">
@@ -610,7 +610,7 @@
       </x:c>
       <x:c r="C10" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
+          <x:t>Carrier enterprise, Parts Received , Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D10" t="inlineStr" s="9">
@@ -1092,21 +1092,21 @@
         </x:is>
       </x:c>
       <x:c r="B19" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1536.7</x:v>
       </x:c>
       <x:c r="C19" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Parts Ordered, PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D19" t="inlineStr" s="9">
         <x:is>
-          <x:t>478958137</x:t>
+          <x:t>587489793</x:t>
         </x:is>
       </x:c>
       <x:c r="E19" t="inlineStr" s="11">
         <x:is>
-          <x:t>478958137</x:t>
+          <x:t>587489793</x:t>
         </x:is>
       </x:c>
       <x:c r="F19" s="13">
@@ -1114,7 +1114,7 @@
       </x:c>
       <x:c r="G19" t="inlineStr" s="15">
         <x:is>
-          <x:t>Ezekiel Mejia-Garcia</x:t>
+          <x:t>PP Tyriq McCall</x:t>
         </x:is>
       </x:c>
       <x:c r="H19" t="inlineStr" s="17">
@@ -1124,19 +1124,19 @@
       </x:c>
       <x:c r="I19" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J19" t="inlineStr" s="21">
         <x:is>
-          <x:t>Sergio Bonadona</x:t>
+          <x:t>PASAMI, LLC</x:t>
         </x:is>
       </x:c>
       <x:c r="K19" s="23">
-        <x:v>45864</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="L19" s="25">
-        <x:v>46106</x:v>
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1146,100 +1146,154 @@
         </x:is>
       </x:c>
       <x:c r="B20" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C20" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D20" t="inlineStr" s="9">
+        <x:is>
+          <x:t>478958137</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E20" t="inlineStr" s="11">
+        <x:is>
+          <x:t>478958137</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F20" s="13">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="G20" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Ezekiel Mejia-Garcia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H20" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I20" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J20" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Sergio Bonadona</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K20" s="23">
+        <x:v>45864</x:v>
+      </x:c>
+      <x:c r="L20" s="25">
+        <x:v>46106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B21" t="n" s="5">
         <x:v>1167.95</x:v>
       </x:c>
-      <x:c r="C20" t="inlineStr" s="7">
+      <x:c r="C21" t="inlineStr" s="7">
         <x:is>
           <x:t>Carrier enterprise, Club Member 3 sys, Parts Ordered</x:t>
         </x:is>
       </x:c>
-      <x:c r="D20" t="inlineStr" s="9">
+      <x:c r="D21" t="inlineStr" s="9">
         <x:is>
           <x:t>587208106</x:t>
         </x:is>
       </x:c>
-      <x:c r="E20" t="inlineStr" s="11">
+      <x:c r="E21" t="inlineStr" s="11">
         <x:is>
           <x:t>587208106</x:t>
         </x:is>
       </x:c>
-      <x:c r="F20" s="13">
+      <x:c r="F21" s="13">
         <x:v>46115</x:v>
       </x:c>
-      <x:c r="G20" t="inlineStr" s="15">
+      <x:c r="G21" t="inlineStr" s="15">
         <x:is>
           <x:t>Michael Kertesz </x:t>
         </x:is>
       </x:c>
-      <x:c r="H20" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I20" t="inlineStr" s="19">
+      <x:c r="H21" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I21" t="inlineStr" s="19">
         <x:is>
           <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
-      <x:c r="J20" t="inlineStr" s="21">
+      <x:c r="J21" t="inlineStr" s="21">
         <x:is>
           <x:t>Brett Frankel</x:t>
         </x:is>
       </x:c>
-      <x:c r="K20" s="23">
+      <x:c r="K21" s="23">
         <x:v>46104</x:v>
       </x:c>
-      <x:c r="L20" s="25">
+      <x:c r="L21" s="25">
         <x:v>46104</x:v>
       </x:c>
     </x:row>
-    <x:row r="21">
-      <x:c r="A21" t="n" s="4">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B21" t="n" s="6">
-        <x:v>590.57631578947368421052631579</x:v>
-      </x:c>
-      <x:c r="C21" t="inlineStr" s="8">
+    <x:row r="22">
+      <x:c r="A22" t="n" s="4">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B22" t="n" s="6">
+        <x:v>637.8825</x:v>
+      </x:c>
+      <x:c r="C22" t="inlineStr" s="8">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D21" t="n" s="10">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E21" t="inlineStr" s="12">
+      <x:c r="D22" t="n" s="10">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E22" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F21" s="14">
+      <x:c r="F22" s="14">
         <x:v/>
       </x:c>
-      <x:c r="G21" t="inlineStr" s="16">
+      <x:c r="G22" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H21" t="inlineStr" s="18">
+      <x:c r="H22" t="inlineStr" s="18">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="I21" t="inlineStr" s="20">
+      <x:c r="I22" t="inlineStr" s="20">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="J21" t="inlineStr" s="22">
+      <x:c r="J22" t="inlineStr" s="22">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="K21" s="24">
+      <x:c r="K22" s="24">
         <x:v/>
       </x:c>
-      <x:c r="L21" s="26">
+      <x:c r="L22" s="26">
         <x:v/>
       </x:c>
     </x:row>

--- a/data/parts_report_future.xlsx
+++ b/data/parts_report_future.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R825f89300db84672"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="R1e9f292fc257427f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R96d3347a7364454a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rd79ee2f06cc74adc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,25 +178,25 @@
       </x:c>
       <x:c r="C2" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
+          <x:t>Club Member, Parts Received , Trane Supply</x:t>
         </x:is>
       </x:c>
       <x:c r="D2" t="inlineStr" s="9">
         <x:is>
-          <x:t>587448096</x:t>
+          <x:t>587375373</x:t>
         </x:is>
       </x:c>
       <x:c r="E2" t="inlineStr" s="11">
         <x:is>
-          <x:t>587448096</x:t>
+          <x:t>587375373</x:t>
         </x:is>
       </x:c>
       <x:c r="F2" s="13">
-        <x:v>46108</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G2" t="inlineStr" s="15">
         <x:is>
-          <x:t/>
+          <x:t>PP Ryley Johnson</x:t>
         </x:is>
       </x:c>
       <x:c r="H2" t="inlineStr" s="17">
@@ -206,12 +206,12 @@
       </x:c>
       <x:c r="I2" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J2" t="inlineStr" s="21">
         <x:is>
-          <x:t>Cassandra Sexton</x:t>
+          <x:t>Laurie Kline</x:t>
         </x:is>
       </x:c>
       <x:c r="K2" s="23">
@@ -228,29 +228,29 @@
         </x:is>
       </x:c>
       <x:c r="B3" t="n" s="5">
-        <x:v>289.85</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C3" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Received </x:t>
+          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member 3 sys, Gemaire, MULTI- 3, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D3" t="inlineStr" s="9">
         <x:is>
-          <x:t>587426826</x:t>
+          <x:t>586595677</x:t>
         </x:is>
       </x:c>
       <x:c r="E3" t="inlineStr" s="11">
         <x:is>
-          <x:t>587426826</x:t>
+          <x:t>586595677</x:t>
         </x:is>
       </x:c>
       <x:c r="F3" s="13">
-        <x:v>46108</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G3" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t>PP Alejandro Espinosa</x:t>
         </x:is>
       </x:c>
       <x:c r="H3" t="inlineStr" s="17">
@@ -260,19 +260,19 @@
       </x:c>
       <x:c r="I3" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J3" t="inlineStr" s="21">
         <x:is>
-          <x:t>Bill Esposito</x:t>
+          <x:t>Bob Lauson</x:t>
         </x:is>
       </x:c>
       <x:c r="K3" s="23">
-        <x:v>46106</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="L3" s="25">
-        <x:v>46106</x:v>
+        <x:v>46098</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -282,29 +282,29 @@
         </x:is>
       </x:c>
       <x:c r="B4" t="n" s="5">
-        <x:v>1248.8</x:v>
+        <x:v>462.83</x:v>
       </x:c>
       <x:c r="C4" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Lennox Supply, Parts Ordered</x:t>
+          <x:t>Baker Supply, Club Member, Parts Ordered, PLM, Potential Membership Renewal, Residential Maintenance Agreement</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" t="inlineStr" s="9">
         <x:is>
-          <x:t>587303898</x:t>
+          <x:t>555552166</x:t>
         </x:is>
       </x:c>
       <x:c r="E4" t="inlineStr" s="11">
         <x:is>
-          <x:t>587303898</x:t>
+          <x:t>555552166</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" s="13">
-        <x:v>46108</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G4" t="inlineStr" s="15">
         <x:is>
-          <x:t>Xavier Mateo</x:t>
+          <x:t>PP Cesar Levy</x:t>
         </x:is>
       </x:c>
       <x:c r="H4" t="inlineStr" s="17">
@@ -314,19 +314,19 @@
       </x:c>
       <x:c r="I4" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J4" t="inlineStr" s="21">
         <x:is>
-          <x:t>ROBERT MCCABE</x:t>
+          <x:t>Wanda Betancourt</x:t>
         </x:is>
       </x:c>
       <x:c r="K4" s="23">
-        <x:v>46105</x:v>
+        <x:v>46007</x:v>
       </x:c>
       <x:c r="L4" s="25">
-        <x:v>46105</x:v>
+        <x:v>46007</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -336,29 +336,29 @@
         </x:is>
       </x:c>
       <x:c r="B5" t="n" s="5">
-        <x:v>1267.95</x:v>
+        <x:v>945.4</x:v>
       </x:c>
       <x:c r="C5" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member 3 sys, Gemaire, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Club Member, Parts Ordered, PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D5" t="inlineStr" s="9">
         <x:is>
-          <x:t>578585007</x:t>
+          <x:t>587403893</x:t>
         </x:is>
       </x:c>
       <x:c r="E5" t="inlineStr" s="11">
         <x:is>
-          <x:t>578585007</x:t>
+          <x:t>587403893</x:t>
         </x:is>
       </x:c>
       <x:c r="F5" s="13">
-        <x:v>46108</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G5" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Cesar Levy</x:t>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H5" t="inlineStr" s="17">
@@ -368,19 +368,19 @@
       </x:c>
       <x:c r="I5" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J5" t="inlineStr" s="21">
         <x:is>
-          <x:t>Serghei Arsentiev</x:t>
+          <x:t>WALKER, CAMERON</x:t>
         </x:is>
       </x:c>
       <x:c r="K5" s="23">
-        <x:v>46037</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L5" s="25">
-        <x:v>46037</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -390,29 +390,29 @@
         </x:is>
       </x:c>
       <x:c r="B6" t="n" s="5">
-        <x:v>292.95</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C6" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Club Member, Parts Ordered, PLM</x:t>
+          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D6" t="inlineStr" s="9">
         <x:is>
-          <x:t>586875916</x:t>
+          <x:t>463016698</x:t>
         </x:is>
       </x:c>
       <x:c r="E6" t="inlineStr" s="11">
         <x:is>
-          <x:t>586875916</x:t>
+          <x:t>463016698</x:t>
         </x:is>
       </x:c>
       <x:c r="F6" s="13">
-        <x:v>46108</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G6" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Barrington Wilson</x:t>
+          <x:t>PP Tyriq McCall</x:t>
         </x:is>
       </x:c>
       <x:c r="H6" t="inlineStr" s="17">
@@ -427,14 +427,14 @@
       </x:c>
       <x:c r="J6" t="inlineStr" s="21">
         <x:is>
-          <x:t>Anna Tyulmenkova</x:t>
+          <x:t>Evan Frangos</x:t>
         </x:is>
       </x:c>
       <x:c r="K6" s="23">
-        <x:v>46100</x:v>
+        <x:v>45762</x:v>
       </x:c>
       <x:c r="L6" s="25">
-        <x:v>46100</x:v>
+        <x:v>45762</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -444,29 +444,29 @@
         </x:is>
       </x:c>
       <x:c r="B7" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>303.45</x:v>
       </x:c>
       <x:c r="C7" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, PLM, Potential Member</x:t>
+          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D7" t="inlineStr" s="9">
         <x:is>
-          <x:t>583259145</x:t>
+          <x:t>581332764</x:t>
         </x:is>
       </x:c>
       <x:c r="E7" t="inlineStr" s="11">
         <x:is>
-          <x:t>583259145</x:t>
+          <x:t>581332764</x:t>
         </x:is>
       </x:c>
       <x:c r="F7" s="13">
-        <x:v>46108</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G7" t="inlineStr" s="15">
         <x:is>
-          <x:t/>
+          <x:t>Justin Greene</x:t>
         </x:is>
       </x:c>
       <x:c r="H7" t="inlineStr" s="17">
@@ -481,14 +481,14 @@
       </x:c>
       <x:c r="J7" t="inlineStr" s="21">
         <x:is>
-          <x:t>John Moore</x:t>
+          <x:t>Chris Orsini</x:t>
         </x:is>
       </x:c>
       <x:c r="K7" s="23">
-        <x:v>46070</x:v>
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L7" s="25">
-        <x:v>46070</x:v>
+        <x:v>46057</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -498,29 +498,29 @@
         </x:is>
       </x:c>
       <x:c r="B8" t="n" s="5">
-        <x:v>2405.92</x:v>
+        <x:v>710.85</x:v>
       </x:c>
       <x:c r="C8" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Parts Ordered, Potential Member</x:t>
+          <x:t>Gemaire, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D8" t="inlineStr" s="9">
         <x:is>
-          <x:t>578394047</x:t>
+          <x:t>580795172</x:t>
         </x:is>
       </x:c>
       <x:c r="E8" t="inlineStr" s="11">
         <x:is>
-          <x:t>578394047</x:t>
+          <x:t>580795172</x:t>
         </x:is>
       </x:c>
       <x:c r="F8" s="13">
-        <x:v>46108</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="G8" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Gurpreet Parihar</x:t>
+          <x:t>PP Alejandro Espinosa</x:t>
         </x:is>
       </x:c>
       <x:c r="H8" t="inlineStr" s="17">
@@ -530,19 +530,19 @@
       </x:c>
       <x:c r="I8" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J8" t="inlineStr" s="21">
         <x:is>
-          <x:t>Edgar Irving</x:t>
+          <x:t>Paul Serota</x:t>
         </x:is>
       </x:c>
       <x:c r="K8" s="23">
-        <x:v>46036</x:v>
+        <x:v>46054</x:v>
       </x:c>
       <x:c r="L8" s="25">
-        <x:v>46036</x:v>
+        <x:v>46054</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -556,25 +556,25 @@
       </x:c>
       <x:c r="C9" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Club Member, Goodman distribution , Parts Ordered</x:t>
+          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D9" t="inlineStr" s="9">
         <x:is>
-          <x:t>585388429</x:t>
+          <x:t>554749130</x:t>
         </x:is>
       </x:c>
       <x:c r="E9" t="inlineStr" s="11">
         <x:is>
-          <x:t>585388429</x:t>
+          <x:t>554749130</x:t>
         </x:is>
       </x:c>
       <x:c r="F9" s="13">
-        <x:v>46108</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="G9" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rickey McClam </x:t>
+          <x:t>Noel Richardson</x:t>
         </x:is>
       </x:c>
       <x:c r="H9" t="inlineStr" s="17">
@@ -589,14 +589,14 @@
       </x:c>
       <x:c r="J9" t="inlineStr" s="21">
         <x:is>
-          <x:t>Charles Funkey</x:t>
+          <x:t>Mildred Rousseau</x:t>
         </x:is>
       </x:c>
       <x:c r="K9" s="23">
-        <x:v>46086</x:v>
+        <x:v>45999</x:v>
       </x:c>
       <x:c r="L9" s="25">
-        <x:v>46086</x:v>
+        <x:v>45999</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -606,29 +606,29 @@
         </x:is>
       </x:c>
       <x:c r="B10" t="n" s="5">
-        <x:v>2125</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C10" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Received , Potential Member</x:t>
+          <x:t>Carrier enterprise, Club Member, Club Member 4 sys, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D10" t="inlineStr" s="9">
         <x:is>
-          <x:t>587416074</x:t>
+          <x:t>586668443</x:t>
         </x:is>
       </x:c>
       <x:c r="E10" t="inlineStr" s="11">
         <x:is>
-          <x:t>587416074</x:t>
+          <x:t>586668443</x:t>
         </x:is>
       </x:c>
       <x:c r="F10" s="13">
-        <x:v>46108</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="G10" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Michael Chenoy</x:t>
+          <x:t>Bruce Coe</x:t>
         </x:is>
       </x:c>
       <x:c r="H10" t="inlineStr" s="17">
@@ -638,19 +638,19 @@
       </x:c>
       <x:c r="I10" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J10" t="inlineStr" s="21">
         <x:is>
-          <x:t>Jian Jia </x:t>
+          <x:t>Harry Leiby</x:t>
         </x:is>
       </x:c>
       <x:c r="K10" s="23">
-        <x:v>46106</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="L10" s="25">
-        <x:v>46106</x:v>
+        <x:v>46098</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -660,29 +660,29 @@
         </x:is>
       </x:c>
       <x:c r="B11" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1536.7</x:v>
       </x:c>
       <x:c r="C11" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Parts Ordered, Trane Supply</x:t>
+          <x:t>Carrier enterprise, Parts Ordered, PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D11" t="inlineStr" s="9">
         <x:is>
-          <x:t>587375373</x:t>
+          <x:t>587489793</x:t>
         </x:is>
       </x:c>
       <x:c r="E11" t="inlineStr" s="11">
         <x:is>
-          <x:t>587375373</x:t>
+          <x:t>587489793</x:t>
         </x:is>
       </x:c>
       <x:c r="F11" s="13">
-        <x:v>46111</x:v>
+        <x:v>46113</x:v>
       </x:c>
       <x:c r="G11" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Ryley Johnson</x:t>
+          <x:t>PP Tyriq McCall</x:t>
         </x:is>
       </x:c>
       <x:c r="H11" t="inlineStr" s="17">
@@ -692,19 +692,19 @@
       </x:c>
       <x:c r="I11" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J11" t="inlineStr" s="21">
         <x:is>
-          <x:t>Laurie Kline</x:t>
+          <x:t>PASAMI, LLC</x:t>
         </x:is>
       </x:c>
       <x:c r="K11" s="23">
-        <x:v>46106</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="L11" s="25">
-        <x:v>46106</x:v>
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -714,29 +714,29 @@
         </x:is>
       </x:c>
       <x:c r="B12" t="n" s="5">
-        <x:v>462.83</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C12" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Club Member, Parts Ordered, PLM, Potential Membership Renewal, Residential Maintenance Agreement</x:t>
+          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D12" t="inlineStr" s="9">
         <x:is>
-          <x:t>555552166</x:t>
+          <x:t>478958137</x:t>
         </x:is>
       </x:c>
       <x:c r="E12" t="inlineStr" s="11">
         <x:is>
-          <x:t>555552166</x:t>
+          <x:t>478958137</x:t>
         </x:is>
       </x:c>
       <x:c r="F12" s="13">
-        <x:v>46111</x:v>
+        <x:v>46113</x:v>
       </x:c>
       <x:c r="G12" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Cesar Levy</x:t>
+          <x:t>Ezekiel Mejia-Garcia</x:t>
         </x:is>
       </x:c>
       <x:c r="H12" t="inlineStr" s="17">
@@ -746,19 +746,19 @@
       </x:c>
       <x:c r="I12" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J12" t="inlineStr" s="21">
         <x:is>
-          <x:t>Wanda Betancourt</x:t>
+          <x:t>Sergio Bonadona</x:t>
         </x:is>
       </x:c>
       <x:c r="K12" s="23">
-        <x:v>46007</x:v>
+        <x:v>45864</x:v>
       </x:c>
       <x:c r="L12" s="25">
-        <x:v>46007</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -768,29 +768,29 @@
         </x:is>
       </x:c>
       <x:c r="B13" t="n" s="5">
-        <x:v>945.4</x:v>
+        <x:v>1167.95</x:v>
       </x:c>
       <x:c r="C13" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Ordered, PLM</x:t>
+          <x:t>Carrier enterprise, Club Member 3 sys, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D13" t="inlineStr" s="9">
         <x:is>
-          <x:t>587403893</x:t>
+          <x:t>587208106</x:t>
         </x:is>
       </x:c>
       <x:c r="E13" t="inlineStr" s="11">
         <x:is>
-          <x:t>587403893</x:t>
+          <x:t>587208106</x:t>
         </x:is>
       </x:c>
       <x:c r="F13" s="13">
-        <x:v>46111</x:v>
+        <x:v>46115</x:v>
       </x:c>
       <x:c r="G13" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t>Michael Kertesz </x:t>
         </x:is>
       </x:c>
       <x:c r="H13" t="inlineStr" s="17">
@@ -805,495 +805,63 @@
       </x:c>
       <x:c r="J13" t="inlineStr" s="21">
         <x:is>
-          <x:t>WALKER, CAMERON</x:t>
+          <x:t>Brett Frankel</x:t>
         </x:is>
       </x:c>
       <x:c r="K13" s="23">
-        <x:v>46106</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="L13" s="25">
-        <x:v>46106</x:v>
+        <x:v>46104</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B14" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C14" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D14" t="inlineStr" s="9">
-        <x:is>
-          <x:t>463016698</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E14" t="inlineStr" s="11">
-        <x:is>
-          <x:t>463016698</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F14" s="13">
-        <x:v>46111</x:v>
-      </x:c>
-      <x:c r="G14" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Tyriq McCall</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H14" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I14" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J14" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Evan Frangos</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K14" s="23">
-        <x:v>45762</x:v>
-      </x:c>
-      <x:c r="L14" s="25">
-        <x:v>45762</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B15" t="n" s="5">
-        <x:v>303.45</x:v>
-      </x:c>
-      <x:c r="C15" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D15" t="inlineStr" s="9">
-        <x:is>
-          <x:t>581332764</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E15" t="inlineStr" s="11">
-        <x:is>
-          <x:t>581332764</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F15" s="13">
-        <x:v>46111</x:v>
-      </x:c>
-      <x:c r="G15" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Justin Greene</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H15" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I15" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J15" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Chris Orsini</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K15" s="23">
-        <x:v>46057</x:v>
-      </x:c>
-      <x:c r="L15" s="25">
-        <x:v>46057</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B16" t="n" s="5">
-        <x:v>710.85</x:v>
-      </x:c>
-      <x:c r="C16" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Gemaire, Parts Ordered, Potential Member</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D16" t="inlineStr" s="9">
-        <x:is>
-          <x:t>580795172</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E16" t="inlineStr" s="11">
-        <x:is>
-          <x:t>580795172</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F16" s="13">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="G16" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H16" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I16" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J16" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Paul Serota</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K16" s="23">
-        <x:v>46054</x:v>
-      </x:c>
-      <x:c r="L16" s="25">
-        <x:v>46054</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B17" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C17" t="inlineStr" s="7">
-        <x:is>
-          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D17" t="inlineStr" s="9">
-        <x:is>
-          <x:t>554749130</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E17" t="inlineStr" s="11">
-        <x:is>
-          <x:t>554749130</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F17" s="13">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="G17" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Noel Richardson</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H17" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I17" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J17" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Mildred Rousseau</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K17" s="23">
-        <x:v>45999</x:v>
-      </x:c>
-      <x:c r="L17" s="25">
-        <x:v>45999</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B18" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C18" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Club Member, Club Member 4 sys, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D18" t="inlineStr" s="9">
-        <x:is>
-          <x:t>586668443</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E18" t="inlineStr" s="11">
-        <x:is>
-          <x:t>586668443</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F18" s="13">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="G18" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Bruce Coe</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H18" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I18" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J18" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Harry Leiby</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K18" s="23">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="L18" s="25">
-        <x:v>46098</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B19" t="n" s="5">
-        <x:v>1536.7</x:v>
-      </x:c>
-      <x:c r="C19" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, PLM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D19" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587489793</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E19" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587489793</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F19" s="13">
-        <x:v>46113</x:v>
-      </x:c>
-      <x:c r="G19" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Tyriq McCall</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H19" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I19" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J19" t="inlineStr" s="21">
-        <x:is>
-          <x:t>PASAMI, LLC</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K19" s="23">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="L19" s="25">
-        <x:v>46107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B20" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C20" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D20" t="inlineStr" s="9">
-        <x:is>
-          <x:t>478958137</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E20" t="inlineStr" s="11">
-        <x:is>
-          <x:t>478958137</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F20" s="13">
-        <x:v>46113</x:v>
-      </x:c>
-      <x:c r="G20" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Ezekiel Mejia-Garcia</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H20" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I20" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J20" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Sergio Bonadona</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K20" s="23">
-        <x:v>45864</x:v>
-      </x:c>
-      <x:c r="L20" s="25">
-        <x:v>46106</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B21" t="n" s="5">
-        <x:v>1167.95</x:v>
-      </x:c>
-      <x:c r="C21" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Club Member 3 sys, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D21" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587208106</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E21" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587208106</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F21" s="13">
-        <x:v>46115</x:v>
-      </x:c>
-      <x:c r="G21" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Michael Kertesz </x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H21" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I21" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J21" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Brett Frankel</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K21" s="23">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="L21" s="25">
-        <x:v>46104</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="n" s="4">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B22" t="n" s="6">
-        <x:v>637.8825</x:v>
-      </x:c>
-      <x:c r="C22" t="inlineStr" s="8">
+      <x:c r="A14" t="n" s="4">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B14" t="n" s="6">
+        <x:v>427.265</x:v>
+      </x:c>
+      <x:c r="C14" t="inlineStr" s="8">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D22" t="n" s="10">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E22" t="inlineStr" s="12">
+      <x:c r="D14" t="n" s="10">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E14" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F22" s="14">
+      <x:c r="F14" s="14">
         <x:v/>
       </x:c>
-      <x:c r="G22" t="inlineStr" s="16">
+      <x:c r="G14" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H22" t="inlineStr" s="18">
+      <x:c r="H14" t="inlineStr" s="18">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="I22" t="inlineStr" s="20">
+      <x:c r="I14" t="inlineStr" s="20">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="J22" t="inlineStr" s="22">
+      <x:c r="J14" t="inlineStr" s="22">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="K22" s="24">
+      <x:c r="K14" s="24">
         <x:v/>
       </x:c>
-      <x:c r="L22" s="26">
+      <x:c r="L14" s="26">
         <x:v/>
       </x:c>
     </x:row>
@@ -1324,7 +892,7 @@
       </x:c>
       <x:c r="B2" t="inlineStr" s="28">
         <x:is>
-          <x:t>03/27/26 - 03/26/27</x:t>
+          <x:t>03/28/26 - 03/27/27</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1390,7 +958,7 @@
     <x:mergeCell ref="A8:B8"/>
   </x:mergeCells>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="hyperlinkId1" location="/new/reports/459565681?DateType=3&amp;BusinessUnitId=2415185%2C2415187%2C15775258%2C2415186%2C2415190%2C182981963%2C182981958%2C182981961%2C182981957&amp;IncludeAdjustmentInvoices=false&amp;IsScheduling=True&amp;From=2026-03-27&amp;To=2027-03-26" display="View Report"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="hyperlinkId1" location="/new/reports/459565681?DateType=3&amp;BusinessUnitId=2415185%2C2415187%2C15775258%2C2415186%2C2415190%2C182981963%2C182981958%2C182981961%2C182981957&amp;IncludeAdjustmentInvoices=false&amp;IsScheduling=True&amp;From=2026-03-28&amp;To=2027-03-27" display="View Report"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/data/parts_report_future.xlsx
+++ b/data/parts_report_future.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R96d3347a7364454a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rd79ee2f06cc74adc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R13e87dce04cc4f87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rec6cd1fef7ee4a60"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/data/parts_report_future.xlsx
+++ b/data/parts_report_future.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R825f89300db84672"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="R1e9f292fc257427f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R13e87dce04cc4f87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rec6cd1fef7ee4a60"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,25 +178,25 @@
       </x:c>
       <x:c r="C2" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
+          <x:t>Club Member, Parts Received , Trane Supply</x:t>
         </x:is>
       </x:c>
       <x:c r="D2" t="inlineStr" s="9">
         <x:is>
-          <x:t>587448096</x:t>
+          <x:t>587375373</x:t>
         </x:is>
       </x:c>
       <x:c r="E2" t="inlineStr" s="11">
         <x:is>
-          <x:t>587448096</x:t>
+          <x:t>587375373</x:t>
         </x:is>
       </x:c>
       <x:c r="F2" s="13">
-        <x:v>46108</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G2" t="inlineStr" s="15">
         <x:is>
-          <x:t/>
+          <x:t>PP Ryley Johnson</x:t>
         </x:is>
       </x:c>
       <x:c r="H2" t="inlineStr" s="17">
@@ -206,12 +206,12 @@
       </x:c>
       <x:c r="I2" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J2" t="inlineStr" s="21">
         <x:is>
-          <x:t>Cassandra Sexton</x:t>
+          <x:t>Laurie Kline</x:t>
         </x:is>
       </x:c>
       <x:c r="K2" s="23">
@@ -228,29 +228,29 @@
         </x:is>
       </x:c>
       <x:c r="B3" t="n" s="5">
-        <x:v>289.85</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C3" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Received </x:t>
+          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member 3 sys, Gemaire, MULTI- 3, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D3" t="inlineStr" s="9">
         <x:is>
-          <x:t>587426826</x:t>
+          <x:t>586595677</x:t>
         </x:is>
       </x:c>
       <x:c r="E3" t="inlineStr" s="11">
         <x:is>
-          <x:t>587426826</x:t>
+          <x:t>586595677</x:t>
         </x:is>
       </x:c>
       <x:c r="F3" s="13">
-        <x:v>46108</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G3" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t>PP Alejandro Espinosa</x:t>
         </x:is>
       </x:c>
       <x:c r="H3" t="inlineStr" s="17">
@@ -260,19 +260,19 @@
       </x:c>
       <x:c r="I3" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J3" t="inlineStr" s="21">
         <x:is>
-          <x:t>Bill Esposito</x:t>
+          <x:t>Bob Lauson</x:t>
         </x:is>
       </x:c>
       <x:c r="K3" s="23">
-        <x:v>46106</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="L3" s="25">
-        <x:v>46106</x:v>
+        <x:v>46098</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -282,29 +282,29 @@
         </x:is>
       </x:c>
       <x:c r="B4" t="n" s="5">
-        <x:v>1248.8</x:v>
+        <x:v>462.83</x:v>
       </x:c>
       <x:c r="C4" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Lennox Supply, Parts Ordered</x:t>
+          <x:t>Baker Supply, Club Member, Parts Ordered, PLM, Potential Membership Renewal, Residential Maintenance Agreement</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" t="inlineStr" s="9">
         <x:is>
-          <x:t>587303898</x:t>
+          <x:t>555552166</x:t>
         </x:is>
       </x:c>
       <x:c r="E4" t="inlineStr" s="11">
         <x:is>
-          <x:t>587303898</x:t>
+          <x:t>555552166</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" s="13">
-        <x:v>46108</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G4" t="inlineStr" s="15">
         <x:is>
-          <x:t>Xavier Mateo</x:t>
+          <x:t>PP Cesar Levy</x:t>
         </x:is>
       </x:c>
       <x:c r="H4" t="inlineStr" s="17">
@@ -314,19 +314,19 @@
       </x:c>
       <x:c r="I4" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J4" t="inlineStr" s="21">
         <x:is>
-          <x:t>ROBERT MCCABE</x:t>
+          <x:t>Wanda Betancourt</x:t>
         </x:is>
       </x:c>
       <x:c r="K4" s="23">
-        <x:v>46105</x:v>
+        <x:v>46007</x:v>
       </x:c>
       <x:c r="L4" s="25">
-        <x:v>46105</x:v>
+        <x:v>46007</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -336,29 +336,29 @@
         </x:is>
       </x:c>
       <x:c r="B5" t="n" s="5">
-        <x:v>1267.95</x:v>
+        <x:v>945.4</x:v>
       </x:c>
       <x:c r="C5" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member 3 sys, Gemaire, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Club Member, Parts Ordered, PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D5" t="inlineStr" s="9">
         <x:is>
-          <x:t>578585007</x:t>
+          <x:t>587403893</x:t>
         </x:is>
       </x:c>
       <x:c r="E5" t="inlineStr" s="11">
         <x:is>
-          <x:t>578585007</x:t>
+          <x:t>587403893</x:t>
         </x:is>
       </x:c>
       <x:c r="F5" s="13">
-        <x:v>46108</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G5" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Cesar Levy</x:t>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H5" t="inlineStr" s="17">
@@ -368,19 +368,19 @@
       </x:c>
       <x:c r="I5" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J5" t="inlineStr" s="21">
         <x:is>
-          <x:t>Serghei Arsentiev</x:t>
+          <x:t>WALKER, CAMERON</x:t>
         </x:is>
       </x:c>
       <x:c r="K5" s="23">
-        <x:v>46037</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L5" s="25">
-        <x:v>46037</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -390,29 +390,29 @@
         </x:is>
       </x:c>
       <x:c r="B6" t="n" s="5">
-        <x:v>292.95</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C6" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Club Member, Parts Ordered, PLM</x:t>
+          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D6" t="inlineStr" s="9">
         <x:is>
-          <x:t>586875916</x:t>
+          <x:t>463016698</x:t>
         </x:is>
       </x:c>
       <x:c r="E6" t="inlineStr" s="11">
         <x:is>
-          <x:t>586875916</x:t>
+          <x:t>463016698</x:t>
         </x:is>
       </x:c>
       <x:c r="F6" s="13">
-        <x:v>46108</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G6" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Barrington Wilson</x:t>
+          <x:t>PP Tyriq McCall</x:t>
         </x:is>
       </x:c>
       <x:c r="H6" t="inlineStr" s="17">
@@ -427,14 +427,14 @@
       </x:c>
       <x:c r="J6" t="inlineStr" s="21">
         <x:is>
-          <x:t>Anna Tyulmenkova</x:t>
+          <x:t>Evan Frangos</x:t>
         </x:is>
       </x:c>
       <x:c r="K6" s="23">
-        <x:v>46100</x:v>
+        <x:v>45762</x:v>
       </x:c>
       <x:c r="L6" s="25">
-        <x:v>46100</x:v>
+        <x:v>45762</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -444,29 +444,29 @@
         </x:is>
       </x:c>
       <x:c r="B7" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>303.45</x:v>
       </x:c>
       <x:c r="C7" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, PLM, Potential Member</x:t>
+          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D7" t="inlineStr" s="9">
         <x:is>
-          <x:t>583259145</x:t>
+          <x:t>581332764</x:t>
         </x:is>
       </x:c>
       <x:c r="E7" t="inlineStr" s="11">
         <x:is>
-          <x:t>583259145</x:t>
+          <x:t>581332764</x:t>
         </x:is>
       </x:c>
       <x:c r="F7" s="13">
-        <x:v>46108</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G7" t="inlineStr" s="15">
         <x:is>
-          <x:t/>
+          <x:t>Justin Greene</x:t>
         </x:is>
       </x:c>
       <x:c r="H7" t="inlineStr" s="17">
@@ -481,14 +481,14 @@
       </x:c>
       <x:c r="J7" t="inlineStr" s="21">
         <x:is>
-          <x:t>John Moore</x:t>
+          <x:t>Chris Orsini</x:t>
         </x:is>
       </x:c>
       <x:c r="K7" s="23">
-        <x:v>46070</x:v>
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L7" s="25">
-        <x:v>46070</x:v>
+        <x:v>46057</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -498,29 +498,29 @@
         </x:is>
       </x:c>
       <x:c r="B8" t="n" s="5">
-        <x:v>2405.92</x:v>
+        <x:v>710.85</x:v>
       </x:c>
       <x:c r="C8" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Parts Ordered, Potential Member</x:t>
+          <x:t>Gemaire, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D8" t="inlineStr" s="9">
         <x:is>
-          <x:t>578394047</x:t>
+          <x:t>580795172</x:t>
         </x:is>
       </x:c>
       <x:c r="E8" t="inlineStr" s="11">
         <x:is>
-          <x:t>578394047</x:t>
+          <x:t>580795172</x:t>
         </x:is>
       </x:c>
       <x:c r="F8" s="13">
-        <x:v>46108</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="G8" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Gurpreet Parihar</x:t>
+          <x:t>PP Alejandro Espinosa</x:t>
         </x:is>
       </x:c>
       <x:c r="H8" t="inlineStr" s="17">
@@ -530,19 +530,19 @@
       </x:c>
       <x:c r="I8" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J8" t="inlineStr" s="21">
         <x:is>
-          <x:t>Edgar Irving</x:t>
+          <x:t>Paul Serota</x:t>
         </x:is>
       </x:c>
       <x:c r="K8" s="23">
-        <x:v>46036</x:v>
+        <x:v>46054</x:v>
       </x:c>
       <x:c r="L8" s="25">
-        <x:v>46036</x:v>
+        <x:v>46054</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -556,25 +556,25 @@
       </x:c>
       <x:c r="C9" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, 10-Year Labor, Club Member, Goodman distribution , Parts Ordered</x:t>
+          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D9" t="inlineStr" s="9">
         <x:is>
-          <x:t>585388429</x:t>
+          <x:t>554749130</x:t>
         </x:is>
       </x:c>
       <x:c r="E9" t="inlineStr" s="11">
         <x:is>
-          <x:t>585388429</x:t>
+          <x:t>554749130</x:t>
         </x:is>
       </x:c>
       <x:c r="F9" s="13">
-        <x:v>46108</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="G9" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rickey McClam </x:t>
+          <x:t>Noel Richardson</x:t>
         </x:is>
       </x:c>
       <x:c r="H9" t="inlineStr" s="17">
@@ -589,14 +589,14 @@
       </x:c>
       <x:c r="J9" t="inlineStr" s="21">
         <x:is>
-          <x:t>Charles Funkey</x:t>
+          <x:t>Mildred Rousseau</x:t>
         </x:is>
       </x:c>
       <x:c r="K9" s="23">
-        <x:v>46086</x:v>
+        <x:v>45999</x:v>
       </x:c>
       <x:c r="L9" s="25">
-        <x:v>46086</x:v>
+        <x:v>45999</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -606,29 +606,29 @@
         </x:is>
       </x:c>
       <x:c r="B10" t="n" s="5">
-        <x:v>2125</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C10" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Received , Potential Member</x:t>
+          <x:t>Carrier enterprise, Club Member, Club Member 4 sys, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D10" t="inlineStr" s="9">
         <x:is>
-          <x:t>587416074</x:t>
+          <x:t>586668443</x:t>
         </x:is>
       </x:c>
       <x:c r="E10" t="inlineStr" s="11">
         <x:is>
-          <x:t>587416074</x:t>
+          <x:t>586668443</x:t>
         </x:is>
       </x:c>
       <x:c r="F10" s="13">
-        <x:v>46108</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="G10" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Michael Chenoy</x:t>
+          <x:t>Bruce Coe</x:t>
         </x:is>
       </x:c>
       <x:c r="H10" t="inlineStr" s="17">
@@ -638,19 +638,19 @@
       </x:c>
       <x:c r="I10" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J10" t="inlineStr" s="21">
         <x:is>
-          <x:t>Jian Jia </x:t>
+          <x:t>Harry Leiby</x:t>
         </x:is>
       </x:c>
       <x:c r="K10" s="23">
-        <x:v>46106</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="L10" s="25">
-        <x:v>46106</x:v>
+        <x:v>46098</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -660,29 +660,29 @@
         </x:is>
       </x:c>
       <x:c r="B11" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1536.7</x:v>
       </x:c>
       <x:c r="C11" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Parts Ordered, Trane Supply</x:t>
+          <x:t>Carrier enterprise, Parts Ordered, PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D11" t="inlineStr" s="9">
         <x:is>
-          <x:t>587375373</x:t>
+          <x:t>587489793</x:t>
         </x:is>
       </x:c>
       <x:c r="E11" t="inlineStr" s="11">
         <x:is>
-          <x:t>587375373</x:t>
+          <x:t>587489793</x:t>
         </x:is>
       </x:c>
       <x:c r="F11" s="13">
-        <x:v>46111</x:v>
+        <x:v>46113</x:v>
       </x:c>
       <x:c r="G11" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Ryley Johnson</x:t>
+          <x:t>PP Tyriq McCall</x:t>
         </x:is>
       </x:c>
       <x:c r="H11" t="inlineStr" s="17">
@@ -692,19 +692,19 @@
       </x:c>
       <x:c r="I11" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J11" t="inlineStr" s="21">
         <x:is>
-          <x:t>Laurie Kline</x:t>
+          <x:t>PASAMI, LLC</x:t>
         </x:is>
       </x:c>
       <x:c r="K11" s="23">
-        <x:v>46106</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="L11" s="25">
-        <x:v>46106</x:v>
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -714,29 +714,29 @@
         </x:is>
       </x:c>
       <x:c r="B12" t="n" s="5">
-        <x:v>462.83</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C12" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Club Member, Parts Ordered, PLM, Potential Membership Renewal, Residential Maintenance Agreement</x:t>
+          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D12" t="inlineStr" s="9">
         <x:is>
-          <x:t>555552166</x:t>
+          <x:t>478958137</x:t>
         </x:is>
       </x:c>
       <x:c r="E12" t="inlineStr" s="11">
         <x:is>
-          <x:t>555552166</x:t>
+          <x:t>478958137</x:t>
         </x:is>
       </x:c>
       <x:c r="F12" s="13">
-        <x:v>46111</x:v>
+        <x:v>46113</x:v>
       </x:c>
       <x:c r="G12" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Cesar Levy</x:t>
+          <x:t>Ezekiel Mejia-Garcia</x:t>
         </x:is>
       </x:c>
       <x:c r="H12" t="inlineStr" s="17">
@@ -746,19 +746,19 @@
       </x:c>
       <x:c r="I12" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J12" t="inlineStr" s="21">
         <x:is>
-          <x:t>Wanda Betancourt</x:t>
+          <x:t>Sergio Bonadona</x:t>
         </x:is>
       </x:c>
       <x:c r="K12" s="23">
-        <x:v>46007</x:v>
+        <x:v>45864</x:v>
       </x:c>
       <x:c r="L12" s="25">
-        <x:v>46007</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -768,29 +768,29 @@
         </x:is>
       </x:c>
       <x:c r="B13" t="n" s="5">
-        <x:v>945.4</x:v>
+        <x:v>1167.95</x:v>
       </x:c>
       <x:c r="C13" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Ordered, PLM</x:t>
+          <x:t>Carrier enterprise, Club Member 3 sys, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D13" t="inlineStr" s="9">
         <x:is>
-          <x:t>587403893</x:t>
+          <x:t>587208106</x:t>
         </x:is>
       </x:c>
       <x:c r="E13" t="inlineStr" s="11">
         <x:is>
-          <x:t>587403893</x:t>
+          <x:t>587208106</x:t>
         </x:is>
       </x:c>
       <x:c r="F13" s="13">
-        <x:v>46111</x:v>
+        <x:v>46115</x:v>
       </x:c>
       <x:c r="G13" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t>Michael Kertesz </x:t>
         </x:is>
       </x:c>
       <x:c r="H13" t="inlineStr" s="17">
@@ -805,495 +805,63 @@
       </x:c>
       <x:c r="J13" t="inlineStr" s="21">
         <x:is>
-          <x:t>WALKER, CAMERON</x:t>
+          <x:t>Brett Frankel</x:t>
         </x:is>
       </x:c>
       <x:c r="K13" s="23">
-        <x:v>46106</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="L13" s="25">
-        <x:v>46106</x:v>
+        <x:v>46104</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B14" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C14" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D14" t="inlineStr" s="9">
-        <x:is>
-          <x:t>463016698</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E14" t="inlineStr" s="11">
-        <x:is>
-          <x:t>463016698</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F14" s="13">
-        <x:v>46111</x:v>
-      </x:c>
-      <x:c r="G14" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Tyriq McCall</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H14" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I14" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J14" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Evan Frangos</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K14" s="23">
-        <x:v>45762</x:v>
-      </x:c>
-      <x:c r="L14" s="25">
-        <x:v>45762</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B15" t="n" s="5">
-        <x:v>303.45</x:v>
-      </x:c>
-      <x:c r="C15" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D15" t="inlineStr" s="9">
-        <x:is>
-          <x:t>581332764</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E15" t="inlineStr" s="11">
-        <x:is>
-          <x:t>581332764</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F15" s="13">
-        <x:v>46111</x:v>
-      </x:c>
-      <x:c r="G15" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Justin Greene</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H15" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I15" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J15" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Chris Orsini</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K15" s="23">
-        <x:v>46057</x:v>
-      </x:c>
-      <x:c r="L15" s="25">
-        <x:v>46057</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B16" t="n" s="5">
-        <x:v>710.85</x:v>
-      </x:c>
-      <x:c r="C16" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Gemaire, Parts Ordered, Potential Member</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D16" t="inlineStr" s="9">
-        <x:is>
-          <x:t>580795172</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E16" t="inlineStr" s="11">
-        <x:is>
-          <x:t>580795172</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F16" s="13">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="G16" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H16" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I16" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J16" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Paul Serota</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K16" s="23">
-        <x:v>46054</x:v>
-      </x:c>
-      <x:c r="L16" s="25">
-        <x:v>46054</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B17" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C17" t="inlineStr" s="7">
-        <x:is>
-          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D17" t="inlineStr" s="9">
-        <x:is>
-          <x:t>554749130</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E17" t="inlineStr" s="11">
-        <x:is>
-          <x:t>554749130</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F17" s="13">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="G17" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Noel Richardson</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H17" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I17" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J17" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Mildred Rousseau</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K17" s="23">
-        <x:v>45999</x:v>
-      </x:c>
-      <x:c r="L17" s="25">
-        <x:v>45999</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B18" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C18" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Club Member, Club Member 4 sys, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D18" t="inlineStr" s="9">
-        <x:is>
-          <x:t>586668443</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E18" t="inlineStr" s="11">
-        <x:is>
-          <x:t>586668443</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F18" s="13">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="G18" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Bruce Coe</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H18" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I18" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J18" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Harry Leiby</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K18" s="23">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="L18" s="25">
-        <x:v>46098</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B19" t="n" s="5">
-        <x:v>1536.7</x:v>
-      </x:c>
-      <x:c r="C19" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, PLM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D19" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587489793</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E19" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587489793</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F19" s="13">
-        <x:v>46113</x:v>
-      </x:c>
-      <x:c r="G19" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Tyriq McCall</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H19" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I19" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J19" t="inlineStr" s="21">
-        <x:is>
-          <x:t>PASAMI, LLC</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K19" s="23">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="L19" s="25">
-        <x:v>46107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B20" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C20" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D20" t="inlineStr" s="9">
-        <x:is>
-          <x:t>478958137</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E20" t="inlineStr" s="11">
-        <x:is>
-          <x:t>478958137</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F20" s="13">
-        <x:v>46113</x:v>
-      </x:c>
-      <x:c r="G20" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Ezekiel Mejia-Garcia</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H20" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I20" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J20" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Sergio Bonadona</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K20" s="23">
-        <x:v>45864</x:v>
-      </x:c>
-      <x:c r="L20" s="25">
-        <x:v>46106</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B21" t="n" s="5">
-        <x:v>1167.95</x:v>
-      </x:c>
-      <x:c r="C21" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Club Member 3 sys, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D21" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587208106</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E21" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587208106</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F21" s="13">
-        <x:v>46115</x:v>
-      </x:c>
-      <x:c r="G21" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Michael Kertesz </x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H21" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I21" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J21" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Brett Frankel</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K21" s="23">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="L21" s="25">
-        <x:v>46104</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="n" s="4">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B22" t="n" s="6">
-        <x:v>637.8825</x:v>
-      </x:c>
-      <x:c r="C22" t="inlineStr" s="8">
+      <x:c r="A14" t="n" s="4">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B14" t="n" s="6">
+        <x:v>427.265</x:v>
+      </x:c>
+      <x:c r="C14" t="inlineStr" s="8">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D22" t="n" s="10">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E22" t="inlineStr" s="12">
+      <x:c r="D14" t="n" s="10">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E14" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F22" s="14">
+      <x:c r="F14" s="14">
         <x:v/>
       </x:c>
-      <x:c r="G22" t="inlineStr" s="16">
+      <x:c r="G14" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H22" t="inlineStr" s="18">
+      <x:c r="H14" t="inlineStr" s="18">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="I22" t="inlineStr" s="20">
+      <x:c r="I14" t="inlineStr" s="20">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="J22" t="inlineStr" s="22">
+      <x:c r="J14" t="inlineStr" s="22">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="K22" s="24">
+      <x:c r="K14" s="24">
         <x:v/>
       </x:c>
-      <x:c r="L22" s="26">
+      <x:c r="L14" s="26">
         <x:v/>
       </x:c>
     </x:row>
@@ -1324,7 +892,7 @@
       </x:c>
       <x:c r="B2" t="inlineStr" s="28">
         <x:is>
-          <x:t>03/27/26 - 03/26/27</x:t>
+          <x:t>03/28/26 - 03/27/27</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1390,7 +958,7 @@
     <x:mergeCell ref="A8:B8"/>
   </x:mergeCells>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="hyperlinkId1" location="/new/reports/459565681?DateType=3&amp;BusinessUnitId=2415185%2C2415187%2C15775258%2C2415186%2C2415190%2C182981963%2C182981958%2C182981961%2C182981957&amp;IncludeAdjustmentInvoices=false&amp;IsScheduling=True&amp;From=2026-03-27&amp;To=2027-03-26" display="View Report"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="hyperlinkId1" location="/new/reports/459565681?DateType=3&amp;BusinessUnitId=2415185%2C2415187%2C15775258%2C2415186%2C2415190%2C182981963%2C182981958%2C182981961%2C182981957&amp;IncludeAdjustmentInvoices=false&amp;IsScheduling=True&amp;From=2026-03-28&amp;To=2027-03-27" display="View Report"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/data/parts_report_future.xlsx
+++ b/data/parts_report_future.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R13e87dce04cc4f87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rec6cd1fef7ee4a60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R96d3347a7364454a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rd79ee2f06cc74adc"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/data/parts_report_future.xlsx
+++ b/data/parts_report_future.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R13e87dce04cc4f87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rec6cd1fef7ee4a60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbff26a604150425d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="R7104b885d45a4b26"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,17 +178,17 @@
       </x:c>
       <x:c r="C2" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Parts Received , Trane Supply</x:t>
+          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member 3 sys, Gemaire, MULTI- 3, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D2" t="inlineStr" s="9">
         <x:is>
-          <x:t>587375373</x:t>
+          <x:t>586595677</x:t>
         </x:is>
       </x:c>
       <x:c r="E2" t="inlineStr" s="11">
         <x:is>
-          <x:t>587375373</x:t>
+          <x:t>586595677</x:t>
         </x:is>
       </x:c>
       <x:c r="F2" s="13">
@@ -196,7 +196,7 @@
       </x:c>
       <x:c r="G2" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Ryley Johnson</x:t>
+          <x:t>PP Alejandro Espinosa</x:t>
         </x:is>
       </x:c>
       <x:c r="H2" t="inlineStr" s="17">
@@ -206,19 +206,19 @@
       </x:c>
       <x:c r="I2" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J2" t="inlineStr" s="21">
         <x:is>
-          <x:t>Laurie Kline</x:t>
+          <x:t>Bob Lauson</x:t>
         </x:is>
       </x:c>
       <x:c r="K2" s="23">
-        <x:v>46106</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="L2" s="25">
-        <x:v>46106</x:v>
+        <x:v>46098</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -228,21 +228,21 @@
         </x:is>
       </x:c>
       <x:c r="B3" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>462.83</x:v>
       </x:c>
       <x:c r="C3" t="inlineStr" s="7">
         <x:is>
-          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member 3 sys, Gemaire, MULTI- 3, Parts Ordered</x:t>
+          <x:t>Baker Supply, Club Member, Parts Ordered, PLM, Potential Membership Renewal, Residential Maintenance Agreement</x:t>
         </x:is>
       </x:c>
       <x:c r="D3" t="inlineStr" s="9">
         <x:is>
-          <x:t>586595677</x:t>
+          <x:t>555552166</x:t>
         </x:is>
       </x:c>
       <x:c r="E3" t="inlineStr" s="11">
         <x:is>
-          <x:t>586595677</x:t>
+          <x:t>555552166</x:t>
         </x:is>
       </x:c>
       <x:c r="F3" s="13">
@@ -250,7 +250,7 @@
       </x:c>
       <x:c r="G3" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
+          <x:t>PP Cesar Levy</x:t>
         </x:is>
       </x:c>
       <x:c r="H3" t="inlineStr" s="17">
@@ -265,14 +265,14 @@
       </x:c>
       <x:c r="J3" t="inlineStr" s="21">
         <x:is>
-          <x:t>Bob Lauson</x:t>
+          <x:t>Wanda Betancourt</x:t>
         </x:is>
       </x:c>
       <x:c r="K3" s="23">
-        <x:v>46098</x:v>
+        <x:v>46007</x:v>
       </x:c>
       <x:c r="L3" s="25">
-        <x:v>46098</x:v>
+        <x:v>46007</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -282,21 +282,21 @@
         </x:is>
       </x:c>
       <x:c r="B4" t="n" s="5">
-        <x:v>462.83</x:v>
+        <x:v>945.4</x:v>
       </x:c>
       <x:c r="C4" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Club Member, Parts Ordered, PLM, Potential Membership Renewal, Residential Maintenance Agreement</x:t>
+          <x:t>Carrier enterprise, Club Member, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" t="inlineStr" s="9">
         <x:is>
-          <x:t>555552166</x:t>
+          <x:t>587403893</x:t>
         </x:is>
       </x:c>
       <x:c r="E4" t="inlineStr" s="11">
         <x:is>
-          <x:t>555552166</x:t>
+          <x:t>587403893</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" s="13">
@@ -304,7 +304,7 @@
       </x:c>
       <x:c r="G4" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Cesar Levy</x:t>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H4" t="inlineStr" s="17">
@@ -319,14 +319,14 @@
       </x:c>
       <x:c r="J4" t="inlineStr" s="21">
         <x:is>
-          <x:t>Wanda Betancourt</x:t>
+          <x:t>WALKER, CAMERON</x:t>
         </x:is>
       </x:c>
       <x:c r="K4" s="23">
-        <x:v>46007</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L4" s="25">
-        <x:v>46007</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -336,21 +336,21 @@
         </x:is>
       </x:c>
       <x:c r="B5" t="n" s="5">
-        <x:v>945.4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C5" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Ordered, PLM</x:t>
+          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D5" t="inlineStr" s="9">
         <x:is>
-          <x:t>587403893</x:t>
+          <x:t>463016698</x:t>
         </x:is>
       </x:c>
       <x:c r="E5" t="inlineStr" s="11">
         <x:is>
-          <x:t>587403893</x:t>
+          <x:t>463016698</x:t>
         </x:is>
       </x:c>
       <x:c r="F5" s="13">
@@ -358,7 +358,7 @@
       </x:c>
       <x:c r="G5" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t>PP Tyriq McCall</x:t>
         </x:is>
       </x:c>
       <x:c r="H5" t="inlineStr" s="17">
@@ -368,19 +368,19 @@
       </x:c>
       <x:c r="I5" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J5" t="inlineStr" s="21">
         <x:is>
-          <x:t>WALKER, CAMERON</x:t>
+          <x:t>Evan Frangos</x:t>
         </x:is>
       </x:c>
       <x:c r="K5" s="23">
-        <x:v>46106</x:v>
+        <x:v>45762</x:v>
       </x:c>
       <x:c r="L5" s="25">
-        <x:v>46106</x:v>
+        <x:v>45762</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -390,21 +390,21 @@
         </x:is>
       </x:c>
       <x:c r="B6" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>303.45</x:v>
       </x:c>
       <x:c r="C6" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D6" t="inlineStr" s="9">
         <x:is>
-          <x:t>463016698</x:t>
+          <x:t>581332764</x:t>
         </x:is>
       </x:c>
       <x:c r="E6" t="inlineStr" s="11">
         <x:is>
-          <x:t>463016698</x:t>
+          <x:t>581332764</x:t>
         </x:is>
       </x:c>
       <x:c r="F6" s="13">
@@ -412,7 +412,7 @@
       </x:c>
       <x:c r="G6" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Tyriq McCall</x:t>
+          <x:t>Justin Greene</x:t>
         </x:is>
       </x:c>
       <x:c r="H6" t="inlineStr" s="17">
@@ -427,14 +427,14 @@
       </x:c>
       <x:c r="J6" t="inlineStr" s="21">
         <x:is>
-          <x:t>Evan Frangos</x:t>
+          <x:t>Chris Orsini</x:t>
         </x:is>
       </x:c>
       <x:c r="K6" s="23">
-        <x:v>45762</x:v>
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L6" s="25">
-        <x:v>45762</x:v>
+        <x:v>46057</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -444,29 +444,29 @@
         </x:is>
       </x:c>
       <x:c r="B7" t="n" s="5">
-        <x:v>303.45</x:v>
+        <x:v>710.85</x:v>
       </x:c>
       <x:c r="C7" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
+          <x:t>Gemaire, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D7" t="inlineStr" s="9">
         <x:is>
-          <x:t>581332764</x:t>
+          <x:t>580795172</x:t>
         </x:is>
       </x:c>
       <x:c r="E7" t="inlineStr" s="11">
         <x:is>
-          <x:t>581332764</x:t>
+          <x:t>580795172</x:t>
         </x:is>
       </x:c>
       <x:c r="F7" s="13">
-        <x:v>46111</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="G7" t="inlineStr" s="15">
         <x:is>
-          <x:t>Justin Greene</x:t>
+          <x:t>PP Alejandro Espinosa</x:t>
         </x:is>
       </x:c>
       <x:c r="H7" t="inlineStr" s="17">
@@ -481,14 +481,14 @@
       </x:c>
       <x:c r="J7" t="inlineStr" s="21">
         <x:is>
-          <x:t>Chris Orsini</x:t>
+          <x:t>Paul Serota</x:t>
         </x:is>
       </x:c>
       <x:c r="K7" s="23">
-        <x:v>46057</x:v>
+        <x:v>46054</x:v>
       </x:c>
       <x:c r="L7" s="25">
-        <x:v>46057</x:v>
+        <x:v>46054</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -498,21 +498,21 @@
         </x:is>
       </x:c>
       <x:c r="B8" t="n" s="5">
-        <x:v>710.85</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C8" t="inlineStr" s="7">
         <x:is>
-          <x:t>Gemaire, Parts Ordered, Potential Member</x:t>
+          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D8" t="inlineStr" s="9">
         <x:is>
-          <x:t>580795172</x:t>
+          <x:t>554749130</x:t>
         </x:is>
       </x:c>
       <x:c r="E8" t="inlineStr" s="11">
         <x:is>
-          <x:t>580795172</x:t>
+          <x:t>554749130</x:t>
         </x:is>
       </x:c>
       <x:c r="F8" s="13">
@@ -520,7 +520,7 @@
       </x:c>
       <x:c r="G8" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
+          <x:t>Noel Richardson</x:t>
         </x:is>
       </x:c>
       <x:c r="H8" t="inlineStr" s="17">
@@ -535,14 +535,14 @@
       </x:c>
       <x:c r="J8" t="inlineStr" s="21">
         <x:is>
-          <x:t>Paul Serota</x:t>
+          <x:t>Mildred Rousseau</x:t>
         </x:is>
       </x:c>
       <x:c r="K8" s="23">
-        <x:v>46054</x:v>
+        <x:v>45999</x:v>
       </x:c>
       <x:c r="L8" s="25">
-        <x:v>46054</x:v>
+        <x:v>45999</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -556,17 +556,17 @@
       </x:c>
       <x:c r="C9" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Club Member, Club Member 4 sys, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D9" t="inlineStr" s="9">
         <x:is>
-          <x:t>554749130</x:t>
+          <x:t>586668443</x:t>
         </x:is>
       </x:c>
       <x:c r="E9" t="inlineStr" s="11">
         <x:is>
-          <x:t>554749130</x:t>
+          <x:t>586668443</x:t>
         </x:is>
       </x:c>
       <x:c r="F9" s="13">
@@ -574,7 +574,7 @@
       </x:c>
       <x:c r="G9" t="inlineStr" s="15">
         <x:is>
-          <x:t>Noel Richardson</x:t>
+          <x:t>Bruce Coe</x:t>
         </x:is>
       </x:c>
       <x:c r="H9" t="inlineStr" s="17">
@@ -589,14 +589,14 @@
       </x:c>
       <x:c r="J9" t="inlineStr" s="21">
         <x:is>
-          <x:t>Mildred Rousseau</x:t>
+          <x:t>Harry Leiby</x:t>
         </x:is>
       </x:c>
       <x:c r="K9" s="23">
-        <x:v>45999</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="L9" s="25">
-        <x:v>45999</x:v>
+        <x:v>46098</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -606,29 +606,29 @@
         </x:is>
       </x:c>
       <x:c r="B10" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1536.7</x:v>
       </x:c>
       <x:c r="C10" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Club Member 4 sys, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Parts Ordered, PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D10" t="inlineStr" s="9">
         <x:is>
-          <x:t>586668443</x:t>
+          <x:t>587489793</x:t>
         </x:is>
       </x:c>
       <x:c r="E10" t="inlineStr" s="11">
         <x:is>
-          <x:t>586668443</x:t>
+          <x:t>587489793</x:t>
         </x:is>
       </x:c>
       <x:c r="F10" s="13">
-        <x:v>46112</x:v>
+        <x:v>46113</x:v>
       </x:c>
       <x:c r="G10" t="inlineStr" s="15">
         <x:is>
-          <x:t>Bruce Coe</x:t>
+          <x:t>PP Tyriq McCall</x:t>
         </x:is>
       </x:c>
       <x:c r="H10" t="inlineStr" s="17">
@@ -638,19 +638,19 @@
       </x:c>
       <x:c r="I10" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J10" t="inlineStr" s="21">
         <x:is>
-          <x:t>Harry Leiby</x:t>
+          <x:t>PASAMI, LLC</x:t>
         </x:is>
       </x:c>
       <x:c r="K10" s="23">
-        <x:v>46098</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="L10" s="25">
-        <x:v>46098</x:v>
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -660,21 +660,21 @@
         </x:is>
       </x:c>
       <x:c r="B11" t="n" s="5">
-        <x:v>1536.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C11" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, PLM</x:t>
+          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D11" t="inlineStr" s="9">
         <x:is>
-          <x:t>587489793</x:t>
+          <x:t>478958137</x:t>
         </x:is>
       </x:c>
       <x:c r="E11" t="inlineStr" s="11">
         <x:is>
-          <x:t>587489793</x:t>
+          <x:t>478958137</x:t>
         </x:is>
       </x:c>
       <x:c r="F11" s="13">
@@ -682,7 +682,7 @@
       </x:c>
       <x:c r="G11" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Tyriq McCall</x:t>
+          <x:t>Ezekiel Mejia-Garcia</x:t>
         </x:is>
       </x:c>
       <x:c r="H11" t="inlineStr" s="17">
@@ -692,19 +692,19 @@
       </x:c>
       <x:c r="I11" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J11" t="inlineStr" s="21">
         <x:is>
-          <x:t>PASAMI, LLC</x:t>
+          <x:t>Sergio Bonadona</x:t>
         </x:is>
       </x:c>
       <x:c r="K11" s="23">
-        <x:v>46107</x:v>
+        <x:v>45864</x:v>
       </x:c>
       <x:c r="L11" s="25">
-        <x:v>46107</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -714,29 +714,29 @@
         </x:is>
       </x:c>
       <x:c r="B12" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1167.95</x:v>
       </x:c>
       <x:c r="C12" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Club Member 3 sys, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D12" t="inlineStr" s="9">
         <x:is>
-          <x:t>478958137</x:t>
+          <x:t>587208106</x:t>
         </x:is>
       </x:c>
       <x:c r="E12" t="inlineStr" s="11">
         <x:is>
-          <x:t>478958137</x:t>
+          <x:t>587208106</x:t>
         </x:is>
       </x:c>
       <x:c r="F12" s="13">
-        <x:v>46113</x:v>
+        <x:v>46115</x:v>
       </x:c>
       <x:c r="G12" t="inlineStr" s="15">
         <x:is>
-          <x:t>Ezekiel Mejia-Garcia</x:t>
+          <x:t>Michael Kertesz </x:t>
         </x:is>
       </x:c>
       <x:c r="H12" t="inlineStr" s="17">
@@ -746,122 +746,68 @@
       </x:c>
       <x:c r="I12" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J12" t="inlineStr" s="21">
         <x:is>
-          <x:t>Sergio Bonadona</x:t>
+          <x:t>Brett Frankel</x:t>
         </x:is>
       </x:c>
       <x:c r="K12" s="23">
-        <x:v>45864</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="L12" s="25">
-        <x:v>46106</x:v>
+        <x:v>46104</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B13" t="n" s="5">
-        <x:v>1167.95</x:v>
-      </x:c>
-      <x:c r="C13" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Club Member 3 sys, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D13" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587208106</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E13" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587208106</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F13" s="13">
-        <x:v>46115</x:v>
-      </x:c>
-      <x:c r="G13" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Michael Kertesz </x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H13" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I13" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J13" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Brett Frankel</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K13" s="23">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="L13" s="25">
-        <x:v>46104</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="n" s="4">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B14" t="n" s="6">
-        <x:v>427.265</x:v>
-      </x:c>
-      <x:c r="C14" t="inlineStr" s="8">
+      <x:c r="A13" t="n" s="4">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B13" t="n" s="6">
+        <x:v>466.10727272727272727272727273</x:v>
+      </x:c>
+      <x:c r="C13" t="inlineStr" s="8">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D14" t="n" s="10">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E14" t="inlineStr" s="12">
+      <x:c r="D13" t="n" s="10">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E13" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F14" s="14">
+      <x:c r="F13" s="14">
         <x:v/>
       </x:c>
-      <x:c r="G14" t="inlineStr" s="16">
+      <x:c r="G13" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H14" t="inlineStr" s="18">
+      <x:c r="H13" t="inlineStr" s="18">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="I14" t="inlineStr" s="20">
+      <x:c r="I13" t="inlineStr" s="20">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="J14" t="inlineStr" s="22">
+      <x:c r="J13" t="inlineStr" s="22">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="K14" s="24">
+      <x:c r="K13" s="24">
         <x:v/>
       </x:c>
-      <x:c r="L14" s="26">
+      <x:c r="L13" s="26">
         <x:v/>
       </x:c>
     </x:row>

--- a/data/parts_report_future.xlsx
+++ b/data/parts_report_future.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R96d3347a7364454a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rd79ee2f06cc74adc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbff26a604150425d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="R7104b885d45a4b26"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,17 +178,17 @@
       </x:c>
       <x:c r="C2" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Parts Received , Trane Supply</x:t>
+          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member 3 sys, Gemaire, MULTI- 3, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D2" t="inlineStr" s="9">
         <x:is>
-          <x:t>587375373</x:t>
+          <x:t>586595677</x:t>
         </x:is>
       </x:c>
       <x:c r="E2" t="inlineStr" s="11">
         <x:is>
-          <x:t>587375373</x:t>
+          <x:t>586595677</x:t>
         </x:is>
       </x:c>
       <x:c r="F2" s="13">
@@ -196,7 +196,7 @@
       </x:c>
       <x:c r="G2" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Ryley Johnson</x:t>
+          <x:t>PP Alejandro Espinosa</x:t>
         </x:is>
       </x:c>
       <x:c r="H2" t="inlineStr" s="17">
@@ -206,19 +206,19 @@
       </x:c>
       <x:c r="I2" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J2" t="inlineStr" s="21">
         <x:is>
-          <x:t>Laurie Kline</x:t>
+          <x:t>Bob Lauson</x:t>
         </x:is>
       </x:c>
       <x:c r="K2" s="23">
-        <x:v>46106</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="L2" s="25">
-        <x:v>46106</x:v>
+        <x:v>46098</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -228,21 +228,21 @@
         </x:is>
       </x:c>
       <x:c r="B3" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>462.83</x:v>
       </x:c>
       <x:c r="C3" t="inlineStr" s="7">
         <x:is>
-          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member 3 sys, Gemaire, MULTI- 3, Parts Ordered</x:t>
+          <x:t>Baker Supply, Club Member, Parts Ordered, PLM, Potential Membership Renewal, Residential Maintenance Agreement</x:t>
         </x:is>
       </x:c>
       <x:c r="D3" t="inlineStr" s="9">
         <x:is>
-          <x:t>586595677</x:t>
+          <x:t>555552166</x:t>
         </x:is>
       </x:c>
       <x:c r="E3" t="inlineStr" s="11">
         <x:is>
-          <x:t>586595677</x:t>
+          <x:t>555552166</x:t>
         </x:is>
       </x:c>
       <x:c r="F3" s="13">
@@ -250,7 +250,7 @@
       </x:c>
       <x:c r="G3" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
+          <x:t>PP Cesar Levy</x:t>
         </x:is>
       </x:c>
       <x:c r="H3" t="inlineStr" s="17">
@@ -265,14 +265,14 @@
       </x:c>
       <x:c r="J3" t="inlineStr" s="21">
         <x:is>
-          <x:t>Bob Lauson</x:t>
+          <x:t>Wanda Betancourt</x:t>
         </x:is>
       </x:c>
       <x:c r="K3" s="23">
-        <x:v>46098</x:v>
+        <x:v>46007</x:v>
       </x:c>
       <x:c r="L3" s="25">
-        <x:v>46098</x:v>
+        <x:v>46007</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -282,21 +282,21 @@
         </x:is>
       </x:c>
       <x:c r="B4" t="n" s="5">
-        <x:v>462.83</x:v>
+        <x:v>945.4</x:v>
       </x:c>
       <x:c r="C4" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Club Member, Parts Ordered, PLM, Potential Membership Renewal, Residential Maintenance Agreement</x:t>
+          <x:t>Carrier enterprise, Club Member, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" t="inlineStr" s="9">
         <x:is>
-          <x:t>555552166</x:t>
+          <x:t>587403893</x:t>
         </x:is>
       </x:c>
       <x:c r="E4" t="inlineStr" s="11">
         <x:is>
-          <x:t>555552166</x:t>
+          <x:t>587403893</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" s="13">
@@ -304,7 +304,7 @@
       </x:c>
       <x:c r="G4" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Cesar Levy</x:t>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H4" t="inlineStr" s="17">
@@ -319,14 +319,14 @@
       </x:c>
       <x:c r="J4" t="inlineStr" s="21">
         <x:is>
-          <x:t>Wanda Betancourt</x:t>
+          <x:t>WALKER, CAMERON</x:t>
         </x:is>
       </x:c>
       <x:c r="K4" s="23">
-        <x:v>46007</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L4" s="25">
-        <x:v>46007</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -336,21 +336,21 @@
         </x:is>
       </x:c>
       <x:c r="B5" t="n" s="5">
-        <x:v>945.4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C5" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Ordered, PLM</x:t>
+          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D5" t="inlineStr" s="9">
         <x:is>
-          <x:t>587403893</x:t>
+          <x:t>463016698</x:t>
         </x:is>
       </x:c>
       <x:c r="E5" t="inlineStr" s="11">
         <x:is>
-          <x:t>587403893</x:t>
+          <x:t>463016698</x:t>
         </x:is>
       </x:c>
       <x:c r="F5" s="13">
@@ -358,7 +358,7 @@
       </x:c>
       <x:c r="G5" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t>PP Tyriq McCall</x:t>
         </x:is>
       </x:c>
       <x:c r="H5" t="inlineStr" s="17">
@@ -368,19 +368,19 @@
       </x:c>
       <x:c r="I5" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J5" t="inlineStr" s="21">
         <x:is>
-          <x:t>WALKER, CAMERON</x:t>
+          <x:t>Evan Frangos</x:t>
         </x:is>
       </x:c>
       <x:c r="K5" s="23">
-        <x:v>46106</x:v>
+        <x:v>45762</x:v>
       </x:c>
       <x:c r="L5" s="25">
-        <x:v>46106</x:v>
+        <x:v>45762</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -390,21 +390,21 @@
         </x:is>
       </x:c>
       <x:c r="B6" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>303.45</x:v>
       </x:c>
       <x:c r="C6" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D6" t="inlineStr" s="9">
         <x:is>
-          <x:t>463016698</x:t>
+          <x:t>581332764</x:t>
         </x:is>
       </x:c>
       <x:c r="E6" t="inlineStr" s="11">
         <x:is>
-          <x:t>463016698</x:t>
+          <x:t>581332764</x:t>
         </x:is>
       </x:c>
       <x:c r="F6" s="13">
@@ -412,7 +412,7 @@
       </x:c>
       <x:c r="G6" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Tyriq McCall</x:t>
+          <x:t>Justin Greene</x:t>
         </x:is>
       </x:c>
       <x:c r="H6" t="inlineStr" s="17">
@@ -427,14 +427,14 @@
       </x:c>
       <x:c r="J6" t="inlineStr" s="21">
         <x:is>
-          <x:t>Evan Frangos</x:t>
+          <x:t>Chris Orsini</x:t>
         </x:is>
       </x:c>
       <x:c r="K6" s="23">
-        <x:v>45762</x:v>
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L6" s="25">
-        <x:v>45762</x:v>
+        <x:v>46057</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -444,29 +444,29 @@
         </x:is>
       </x:c>
       <x:c r="B7" t="n" s="5">
-        <x:v>303.45</x:v>
+        <x:v>710.85</x:v>
       </x:c>
       <x:c r="C7" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
+          <x:t>Gemaire, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D7" t="inlineStr" s="9">
         <x:is>
-          <x:t>581332764</x:t>
+          <x:t>580795172</x:t>
         </x:is>
       </x:c>
       <x:c r="E7" t="inlineStr" s="11">
         <x:is>
-          <x:t>581332764</x:t>
+          <x:t>580795172</x:t>
         </x:is>
       </x:c>
       <x:c r="F7" s="13">
-        <x:v>46111</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="G7" t="inlineStr" s="15">
         <x:is>
-          <x:t>Justin Greene</x:t>
+          <x:t>PP Alejandro Espinosa</x:t>
         </x:is>
       </x:c>
       <x:c r="H7" t="inlineStr" s="17">
@@ -481,14 +481,14 @@
       </x:c>
       <x:c r="J7" t="inlineStr" s="21">
         <x:is>
-          <x:t>Chris Orsini</x:t>
+          <x:t>Paul Serota</x:t>
         </x:is>
       </x:c>
       <x:c r="K7" s="23">
-        <x:v>46057</x:v>
+        <x:v>46054</x:v>
       </x:c>
       <x:c r="L7" s="25">
-        <x:v>46057</x:v>
+        <x:v>46054</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -498,21 +498,21 @@
         </x:is>
       </x:c>
       <x:c r="B8" t="n" s="5">
-        <x:v>710.85</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C8" t="inlineStr" s="7">
         <x:is>
-          <x:t>Gemaire, Parts Ordered, Potential Member</x:t>
+          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D8" t="inlineStr" s="9">
         <x:is>
-          <x:t>580795172</x:t>
+          <x:t>554749130</x:t>
         </x:is>
       </x:c>
       <x:c r="E8" t="inlineStr" s="11">
         <x:is>
-          <x:t>580795172</x:t>
+          <x:t>554749130</x:t>
         </x:is>
       </x:c>
       <x:c r="F8" s="13">
@@ -520,7 +520,7 @@
       </x:c>
       <x:c r="G8" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
+          <x:t>Noel Richardson</x:t>
         </x:is>
       </x:c>
       <x:c r="H8" t="inlineStr" s="17">
@@ -535,14 +535,14 @@
       </x:c>
       <x:c r="J8" t="inlineStr" s="21">
         <x:is>
-          <x:t>Paul Serota</x:t>
+          <x:t>Mildred Rousseau</x:t>
         </x:is>
       </x:c>
       <x:c r="K8" s="23">
-        <x:v>46054</x:v>
+        <x:v>45999</x:v>
       </x:c>
       <x:c r="L8" s="25">
-        <x:v>46054</x:v>
+        <x:v>45999</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -556,17 +556,17 @@
       </x:c>
       <x:c r="C9" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Club Member, Club Member 4 sys, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D9" t="inlineStr" s="9">
         <x:is>
-          <x:t>554749130</x:t>
+          <x:t>586668443</x:t>
         </x:is>
       </x:c>
       <x:c r="E9" t="inlineStr" s="11">
         <x:is>
-          <x:t>554749130</x:t>
+          <x:t>586668443</x:t>
         </x:is>
       </x:c>
       <x:c r="F9" s="13">
@@ -574,7 +574,7 @@
       </x:c>
       <x:c r="G9" t="inlineStr" s="15">
         <x:is>
-          <x:t>Noel Richardson</x:t>
+          <x:t>Bruce Coe</x:t>
         </x:is>
       </x:c>
       <x:c r="H9" t="inlineStr" s="17">
@@ -589,14 +589,14 @@
       </x:c>
       <x:c r="J9" t="inlineStr" s="21">
         <x:is>
-          <x:t>Mildred Rousseau</x:t>
+          <x:t>Harry Leiby</x:t>
         </x:is>
       </x:c>
       <x:c r="K9" s="23">
-        <x:v>45999</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="L9" s="25">
-        <x:v>45999</x:v>
+        <x:v>46098</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -606,29 +606,29 @@
         </x:is>
       </x:c>
       <x:c r="B10" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1536.7</x:v>
       </x:c>
       <x:c r="C10" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Club Member 4 sys, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Parts Ordered, PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D10" t="inlineStr" s="9">
         <x:is>
-          <x:t>586668443</x:t>
+          <x:t>587489793</x:t>
         </x:is>
       </x:c>
       <x:c r="E10" t="inlineStr" s="11">
         <x:is>
-          <x:t>586668443</x:t>
+          <x:t>587489793</x:t>
         </x:is>
       </x:c>
       <x:c r="F10" s="13">
-        <x:v>46112</x:v>
+        <x:v>46113</x:v>
       </x:c>
       <x:c r="G10" t="inlineStr" s="15">
         <x:is>
-          <x:t>Bruce Coe</x:t>
+          <x:t>PP Tyriq McCall</x:t>
         </x:is>
       </x:c>
       <x:c r="H10" t="inlineStr" s="17">
@@ -638,19 +638,19 @@
       </x:c>
       <x:c r="I10" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J10" t="inlineStr" s="21">
         <x:is>
-          <x:t>Harry Leiby</x:t>
+          <x:t>PASAMI, LLC</x:t>
         </x:is>
       </x:c>
       <x:c r="K10" s="23">
-        <x:v>46098</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="L10" s="25">
-        <x:v>46098</x:v>
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -660,21 +660,21 @@
         </x:is>
       </x:c>
       <x:c r="B11" t="n" s="5">
-        <x:v>1536.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C11" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, PLM</x:t>
+          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D11" t="inlineStr" s="9">
         <x:is>
-          <x:t>587489793</x:t>
+          <x:t>478958137</x:t>
         </x:is>
       </x:c>
       <x:c r="E11" t="inlineStr" s="11">
         <x:is>
-          <x:t>587489793</x:t>
+          <x:t>478958137</x:t>
         </x:is>
       </x:c>
       <x:c r="F11" s="13">
@@ -682,7 +682,7 @@
       </x:c>
       <x:c r="G11" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Tyriq McCall</x:t>
+          <x:t>Ezekiel Mejia-Garcia</x:t>
         </x:is>
       </x:c>
       <x:c r="H11" t="inlineStr" s="17">
@@ -692,19 +692,19 @@
       </x:c>
       <x:c r="I11" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J11" t="inlineStr" s="21">
         <x:is>
-          <x:t>PASAMI, LLC</x:t>
+          <x:t>Sergio Bonadona</x:t>
         </x:is>
       </x:c>
       <x:c r="K11" s="23">
-        <x:v>46107</x:v>
+        <x:v>45864</x:v>
       </x:c>
       <x:c r="L11" s="25">
-        <x:v>46107</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -714,29 +714,29 @@
         </x:is>
       </x:c>
       <x:c r="B12" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1167.95</x:v>
       </x:c>
       <x:c r="C12" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Club Member 3 sys, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D12" t="inlineStr" s="9">
         <x:is>
-          <x:t>478958137</x:t>
+          <x:t>587208106</x:t>
         </x:is>
       </x:c>
       <x:c r="E12" t="inlineStr" s="11">
         <x:is>
-          <x:t>478958137</x:t>
+          <x:t>587208106</x:t>
         </x:is>
       </x:c>
       <x:c r="F12" s="13">
-        <x:v>46113</x:v>
+        <x:v>46115</x:v>
       </x:c>
       <x:c r="G12" t="inlineStr" s="15">
         <x:is>
-          <x:t>Ezekiel Mejia-Garcia</x:t>
+          <x:t>Michael Kertesz </x:t>
         </x:is>
       </x:c>
       <x:c r="H12" t="inlineStr" s="17">
@@ -746,122 +746,68 @@
       </x:c>
       <x:c r="I12" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J12" t="inlineStr" s="21">
         <x:is>
-          <x:t>Sergio Bonadona</x:t>
+          <x:t>Brett Frankel</x:t>
         </x:is>
       </x:c>
       <x:c r="K12" s="23">
-        <x:v>45864</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="L12" s="25">
-        <x:v>46106</x:v>
+        <x:v>46104</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B13" t="n" s="5">
-        <x:v>1167.95</x:v>
-      </x:c>
-      <x:c r="C13" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Club Member 3 sys, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D13" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587208106</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E13" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587208106</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F13" s="13">
-        <x:v>46115</x:v>
-      </x:c>
-      <x:c r="G13" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Michael Kertesz </x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H13" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I13" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J13" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Brett Frankel</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K13" s="23">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="L13" s="25">
-        <x:v>46104</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="n" s="4">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B14" t="n" s="6">
-        <x:v>427.265</x:v>
-      </x:c>
-      <x:c r="C14" t="inlineStr" s="8">
+      <x:c r="A13" t="n" s="4">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B13" t="n" s="6">
+        <x:v>466.10727272727272727272727273</x:v>
+      </x:c>
+      <x:c r="C13" t="inlineStr" s="8">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D14" t="n" s="10">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E14" t="inlineStr" s="12">
+      <x:c r="D13" t="n" s="10">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E13" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F14" s="14">
+      <x:c r="F13" s="14">
         <x:v/>
       </x:c>
-      <x:c r="G14" t="inlineStr" s="16">
+      <x:c r="G13" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H14" t="inlineStr" s="18">
+      <x:c r="H13" t="inlineStr" s="18">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="I14" t="inlineStr" s="20">
+      <x:c r="I13" t="inlineStr" s="20">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="J14" t="inlineStr" s="22">
+      <x:c r="J13" t="inlineStr" s="22">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="K14" s="24">
+      <x:c r="K13" s="24">
         <x:v/>
       </x:c>
-      <x:c r="L14" s="26">
+      <x:c r="L13" s="26">
         <x:v/>
       </x:c>
     </x:row>

--- a/data/parts_report_future.xlsx
+++ b/data/parts_report_future.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbff26a604150425d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="R7104b885d45a4b26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6532c83e54804366"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="R9b2b33f7224f4bc8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,17 +178,17 @@
       </x:c>
       <x:c r="C2" t="inlineStr" s="7">
         <x:is>
-          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member 3 sys, Gemaire, MULTI- 3, Parts Ordered</x:t>
+          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D2" t="inlineStr" s="9">
         <x:is>
-          <x:t>586595677</x:t>
+          <x:t>587794082</x:t>
         </x:is>
       </x:c>
       <x:c r="E2" t="inlineStr" s="11">
         <x:is>
-          <x:t>586595677</x:t>
+          <x:t>587794082</x:t>
         </x:is>
       </x:c>
       <x:c r="F2" s="13">
@@ -196,7 +196,7 @@
       </x:c>
       <x:c r="G2" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
+          <x:t>Tyler Gallatin</x:t>
         </x:is>
       </x:c>
       <x:c r="H2" t="inlineStr" s="17">
@@ -206,19 +206,19 @@
       </x:c>
       <x:c r="I2" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J2" t="inlineStr" s="21">
         <x:is>
-          <x:t>Bob Lauson</x:t>
+          <x:t>Louise Claydon</x:t>
         </x:is>
       </x:c>
       <x:c r="K2" s="23">
-        <x:v>46098</x:v>
+        <x:v>46110</x:v>
       </x:c>
       <x:c r="L2" s="25">
-        <x:v>46098</x:v>
+        <x:v>46110</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -228,21 +228,21 @@
         </x:is>
       </x:c>
       <x:c r="B3" t="n" s="5">
-        <x:v>462.83</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C3" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Club Member, Parts Ordered, PLM, Potential Membership Renewal, Residential Maintenance Agreement</x:t>
+          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member 3 sys, Gemaire, MULTI- 3, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D3" t="inlineStr" s="9">
         <x:is>
-          <x:t>555552166</x:t>
+          <x:t>586595677</x:t>
         </x:is>
       </x:c>
       <x:c r="E3" t="inlineStr" s="11">
         <x:is>
-          <x:t>555552166</x:t>
+          <x:t>586595677</x:t>
         </x:is>
       </x:c>
       <x:c r="F3" s="13">
@@ -250,7 +250,7 @@
       </x:c>
       <x:c r="G3" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Cesar Levy</x:t>
+          <x:t>PP Alejandro Espinosa</x:t>
         </x:is>
       </x:c>
       <x:c r="H3" t="inlineStr" s="17">
@@ -265,14 +265,14 @@
       </x:c>
       <x:c r="J3" t="inlineStr" s="21">
         <x:is>
-          <x:t>Wanda Betancourt</x:t>
+          <x:t>Bob Lauson</x:t>
         </x:is>
       </x:c>
       <x:c r="K3" s="23">
-        <x:v>46007</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="L3" s="25">
-        <x:v>46007</x:v>
+        <x:v>46098</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -282,21 +282,21 @@
         </x:is>
       </x:c>
       <x:c r="B4" t="n" s="5">
-        <x:v>945.4</x:v>
+        <x:v>462.83</x:v>
       </x:c>
       <x:c r="C4" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Received , PLM</x:t>
+          <x:t>Baker Supply, Club Member, Parts Ordered, PLM, Potential Membership Renewal, Residential Maintenance Agreement</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" t="inlineStr" s="9">
         <x:is>
-          <x:t>587403893</x:t>
+          <x:t>555552166</x:t>
         </x:is>
       </x:c>
       <x:c r="E4" t="inlineStr" s="11">
         <x:is>
-          <x:t>587403893</x:t>
+          <x:t>555552166</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" s="13">
@@ -304,7 +304,7 @@
       </x:c>
       <x:c r="G4" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t>PP Cesar Levy</x:t>
         </x:is>
       </x:c>
       <x:c r="H4" t="inlineStr" s="17">
@@ -319,14 +319,14 @@
       </x:c>
       <x:c r="J4" t="inlineStr" s="21">
         <x:is>
-          <x:t>WALKER, CAMERON</x:t>
+          <x:t>Wanda Betancourt</x:t>
         </x:is>
       </x:c>
       <x:c r="K4" s="23">
-        <x:v>46106</x:v>
+        <x:v>46007</x:v>
       </x:c>
       <x:c r="L4" s="25">
-        <x:v>46106</x:v>
+        <x:v>46007</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -336,21 +336,21 @@
         </x:is>
       </x:c>
       <x:c r="B5" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>945.4</x:v>
       </x:c>
       <x:c r="C5" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Club Member, Parts Received , PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D5" t="inlineStr" s="9">
         <x:is>
-          <x:t>463016698</x:t>
+          <x:t>587403893</x:t>
         </x:is>
       </x:c>
       <x:c r="E5" t="inlineStr" s="11">
         <x:is>
-          <x:t>463016698</x:t>
+          <x:t>587403893</x:t>
         </x:is>
       </x:c>
       <x:c r="F5" s="13">
@@ -358,7 +358,7 @@
       </x:c>
       <x:c r="G5" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Tyriq McCall</x:t>
+          <x:t>Rolin Moimeme</x:t>
         </x:is>
       </x:c>
       <x:c r="H5" t="inlineStr" s="17">
@@ -368,19 +368,19 @@
       </x:c>
       <x:c r="I5" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J5" t="inlineStr" s="21">
         <x:is>
-          <x:t>Evan Frangos</x:t>
+          <x:t>WALKER, CAMERON</x:t>
         </x:is>
       </x:c>
       <x:c r="K5" s="23">
-        <x:v>45762</x:v>
+        <x:v>46106</x:v>
       </x:c>
       <x:c r="L5" s="25">
-        <x:v>45762</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -390,21 +390,21 @@
         </x:is>
       </x:c>
       <x:c r="B6" t="n" s="5">
-        <x:v>303.45</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C6" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
+          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D6" t="inlineStr" s="9">
         <x:is>
-          <x:t>581332764</x:t>
+          <x:t>463016698</x:t>
         </x:is>
       </x:c>
       <x:c r="E6" t="inlineStr" s="11">
         <x:is>
-          <x:t>581332764</x:t>
+          <x:t>463016698</x:t>
         </x:is>
       </x:c>
       <x:c r="F6" s="13">
@@ -412,7 +412,7 @@
       </x:c>
       <x:c r="G6" t="inlineStr" s="15">
         <x:is>
-          <x:t>Justin Greene</x:t>
+          <x:t>PP Tyriq McCall</x:t>
         </x:is>
       </x:c>
       <x:c r="H6" t="inlineStr" s="17">
@@ -427,14 +427,14 @@
       </x:c>
       <x:c r="J6" t="inlineStr" s="21">
         <x:is>
-          <x:t>Chris Orsini</x:t>
+          <x:t>Evan Frangos</x:t>
         </x:is>
       </x:c>
       <x:c r="K6" s="23">
-        <x:v>46057</x:v>
+        <x:v>45762</x:v>
       </x:c>
       <x:c r="L6" s="25">
-        <x:v>46057</x:v>
+        <x:v>45762</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -444,29 +444,29 @@
         </x:is>
       </x:c>
       <x:c r="B7" t="n" s="5">
-        <x:v>710.85</x:v>
+        <x:v>303.45</x:v>
       </x:c>
       <x:c r="C7" t="inlineStr" s="7">
         <x:is>
-          <x:t>Gemaire, Parts Ordered, Potential Member</x:t>
+          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D7" t="inlineStr" s="9">
         <x:is>
-          <x:t>580795172</x:t>
+          <x:t>581332764</x:t>
         </x:is>
       </x:c>
       <x:c r="E7" t="inlineStr" s="11">
         <x:is>
-          <x:t>580795172</x:t>
+          <x:t>581332764</x:t>
         </x:is>
       </x:c>
       <x:c r="F7" s="13">
-        <x:v>46112</x:v>
+        <x:v>46111</x:v>
       </x:c>
       <x:c r="G7" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
+          <x:t>Justin Greene</x:t>
         </x:is>
       </x:c>
       <x:c r="H7" t="inlineStr" s="17">
@@ -481,14 +481,14 @@
       </x:c>
       <x:c r="J7" t="inlineStr" s="21">
         <x:is>
-          <x:t>Paul Serota</x:t>
+          <x:t>Chris Orsini</x:t>
         </x:is>
       </x:c>
       <x:c r="K7" s="23">
-        <x:v>46054</x:v>
+        <x:v>46057</x:v>
       </x:c>
       <x:c r="L7" s="25">
-        <x:v>46054</x:v>
+        <x:v>46057</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -498,21 +498,21 @@
         </x:is>
       </x:c>
       <x:c r="B8" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>710.85</x:v>
       </x:c>
       <x:c r="C8" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
+          <x:t>Gemaire, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D8" t="inlineStr" s="9">
         <x:is>
-          <x:t>554749130</x:t>
+          <x:t>580795172</x:t>
         </x:is>
       </x:c>
       <x:c r="E8" t="inlineStr" s="11">
         <x:is>
-          <x:t>554749130</x:t>
+          <x:t>580795172</x:t>
         </x:is>
       </x:c>
       <x:c r="F8" s="13">
@@ -520,7 +520,7 @@
       </x:c>
       <x:c r="G8" t="inlineStr" s="15">
         <x:is>
-          <x:t>Noel Richardson</x:t>
+          <x:t>PP Alejandro Espinosa</x:t>
         </x:is>
       </x:c>
       <x:c r="H8" t="inlineStr" s="17">
@@ -535,14 +535,14 @@
       </x:c>
       <x:c r="J8" t="inlineStr" s="21">
         <x:is>
-          <x:t>Mildred Rousseau</x:t>
+          <x:t>Paul Serota</x:t>
         </x:is>
       </x:c>
       <x:c r="K8" s="23">
-        <x:v>45999</x:v>
+        <x:v>46054</x:v>
       </x:c>
       <x:c r="L8" s="25">
-        <x:v>45999</x:v>
+        <x:v>46054</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -556,17 +556,17 @@
       </x:c>
       <x:c r="C9" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Club Member 4 sys, Parts Ordered</x:t>
+          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D9" t="inlineStr" s="9">
         <x:is>
-          <x:t>586668443</x:t>
+          <x:t>554749130</x:t>
         </x:is>
       </x:c>
       <x:c r="E9" t="inlineStr" s="11">
         <x:is>
-          <x:t>586668443</x:t>
+          <x:t>554749130</x:t>
         </x:is>
       </x:c>
       <x:c r="F9" s="13">
@@ -574,7 +574,7 @@
       </x:c>
       <x:c r="G9" t="inlineStr" s="15">
         <x:is>
-          <x:t>Bruce Coe</x:t>
+          <x:t>Noel Richardson</x:t>
         </x:is>
       </x:c>
       <x:c r="H9" t="inlineStr" s="17">
@@ -589,14 +589,14 @@
       </x:c>
       <x:c r="J9" t="inlineStr" s="21">
         <x:is>
-          <x:t>Harry Leiby</x:t>
+          <x:t>Mildred Rousseau</x:t>
         </x:is>
       </x:c>
       <x:c r="K9" s="23">
-        <x:v>46098</x:v>
+        <x:v>45999</x:v>
       </x:c>
       <x:c r="L9" s="25">
-        <x:v>46098</x:v>
+        <x:v>45999</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -606,29 +606,29 @@
         </x:is>
       </x:c>
       <x:c r="B10" t="n" s="5">
-        <x:v>1536.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C10" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, PLM</x:t>
+          <x:t>Carrier enterprise, Club Member, Club Member 4 sys, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D10" t="inlineStr" s="9">
         <x:is>
-          <x:t>587489793</x:t>
+          <x:t>586668443</x:t>
         </x:is>
       </x:c>
       <x:c r="E10" t="inlineStr" s="11">
         <x:is>
-          <x:t>587489793</x:t>
+          <x:t>586668443</x:t>
         </x:is>
       </x:c>
       <x:c r="F10" s="13">
-        <x:v>46113</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="G10" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Tyriq McCall</x:t>
+          <x:t>Bruce Coe</x:t>
         </x:is>
       </x:c>
       <x:c r="H10" t="inlineStr" s="17">
@@ -638,19 +638,19 @@
       </x:c>
       <x:c r="I10" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J10" t="inlineStr" s="21">
         <x:is>
-          <x:t>PASAMI, LLC</x:t>
+          <x:t>Harry Leiby</x:t>
         </x:is>
       </x:c>
       <x:c r="K10" s="23">
-        <x:v>46107</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="L10" s="25">
-        <x:v>46107</x:v>
+        <x:v>46098</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -660,21 +660,21 @@
         </x:is>
       </x:c>
       <x:c r="B11" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>1536.7</x:v>
       </x:c>
       <x:c r="C11" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Parts Ordered, PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D11" t="inlineStr" s="9">
         <x:is>
-          <x:t>478958137</x:t>
+          <x:t>587489793</x:t>
         </x:is>
       </x:c>
       <x:c r="E11" t="inlineStr" s="11">
         <x:is>
-          <x:t>478958137</x:t>
+          <x:t>587489793</x:t>
         </x:is>
       </x:c>
       <x:c r="F11" s="13">
@@ -682,7 +682,7 @@
       </x:c>
       <x:c r="G11" t="inlineStr" s="15">
         <x:is>
-          <x:t>Ezekiel Mejia-Garcia</x:t>
+          <x:t>PP Tyriq McCall</x:t>
         </x:is>
       </x:c>
       <x:c r="H11" t="inlineStr" s="17">
@@ -692,19 +692,19 @@
       </x:c>
       <x:c r="I11" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J11" t="inlineStr" s="21">
         <x:is>
-          <x:t>Sergio Bonadona</x:t>
+          <x:t>PASAMI, LLC</x:t>
         </x:is>
       </x:c>
       <x:c r="K11" s="23">
-        <x:v>45864</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="L11" s="25">
-        <x:v>46106</x:v>
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -714,100 +714,154 @@
         </x:is>
       </x:c>
       <x:c r="B12" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C12" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" t="inlineStr" s="9">
+        <x:is>
+          <x:t>478958137</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" t="inlineStr" s="11">
+        <x:is>
+          <x:t>478958137</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F12" s="13">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="G12" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Ezekiel Mejia-Garcia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H12" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I12" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J12" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Sergio Bonadona</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K12" s="23">
+        <x:v>45864</x:v>
+      </x:c>
+      <x:c r="L12" s="25">
+        <x:v>46106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" t="n" s="5">
         <x:v>1167.95</x:v>
       </x:c>
-      <x:c r="C12" t="inlineStr" s="7">
+      <x:c r="C13" t="inlineStr" s="7">
         <x:is>
           <x:t>Carrier enterprise, Club Member 3 sys, Parts Ordered</x:t>
         </x:is>
       </x:c>
-      <x:c r="D12" t="inlineStr" s="9">
+      <x:c r="D13" t="inlineStr" s="9">
         <x:is>
           <x:t>587208106</x:t>
         </x:is>
       </x:c>
-      <x:c r="E12" t="inlineStr" s="11">
+      <x:c r="E13" t="inlineStr" s="11">
         <x:is>
           <x:t>587208106</x:t>
         </x:is>
       </x:c>
-      <x:c r="F12" s="13">
+      <x:c r="F13" s="13">
         <x:v>46115</x:v>
       </x:c>
-      <x:c r="G12" t="inlineStr" s="15">
+      <x:c r="G13" t="inlineStr" s="15">
         <x:is>
           <x:t>Michael Kertesz </x:t>
         </x:is>
       </x:c>
-      <x:c r="H12" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I12" t="inlineStr" s="19">
+      <x:c r="H13" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I13" t="inlineStr" s="19">
         <x:is>
           <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
-      <x:c r="J12" t="inlineStr" s="21">
+      <x:c r="J13" t="inlineStr" s="21">
         <x:is>
           <x:t>Brett Frankel</x:t>
         </x:is>
       </x:c>
-      <x:c r="K12" s="23">
+      <x:c r="K13" s="23">
         <x:v>46104</x:v>
       </x:c>
-      <x:c r="L12" s="25">
+      <x:c r="L13" s="25">
         <x:v>46104</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="n" s="4">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B13" t="n" s="6">
-        <x:v>466.10727272727272727272727273</x:v>
-      </x:c>
-      <x:c r="C13" t="inlineStr" s="8">
+    <x:row r="14">
+      <x:c r="A14" t="n" s="4">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B14" t="n" s="6">
+        <x:v>427.265</x:v>
+      </x:c>
+      <x:c r="C14" t="inlineStr" s="8">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D13" t="n" s="10">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E13" t="inlineStr" s="12">
+      <x:c r="D14" t="n" s="10">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E14" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F13" s="14">
+      <x:c r="F14" s="14">
         <x:v/>
       </x:c>
-      <x:c r="G13" t="inlineStr" s="16">
+      <x:c r="G14" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H13" t="inlineStr" s="18">
+      <x:c r="H14" t="inlineStr" s="18">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="I13" t="inlineStr" s="20">
+      <x:c r="I14" t="inlineStr" s="20">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="J13" t="inlineStr" s="22">
+      <x:c r="J14" t="inlineStr" s="22">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="K13" s="24">
+      <x:c r="K14" s="24">
         <x:v/>
       </x:c>
-      <x:c r="L13" s="26">
+      <x:c r="L14" s="26">
         <x:v/>
       </x:c>
     </x:row>
@@ -838,7 +892,7 @@
       </x:c>
       <x:c r="B2" t="inlineStr" s="28">
         <x:is>
-          <x:t>03/28/26 - 03/27/27</x:t>
+          <x:t>03/30/26 - 03/29/27</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -904,7 +958,7 @@
     <x:mergeCell ref="A8:B8"/>
   </x:mergeCells>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="hyperlinkId1" location="/new/reports/459565681?DateType=3&amp;BusinessUnitId=2415185%2C2415187%2C15775258%2C2415186%2C2415190%2C182981963%2C182981958%2C182981961%2C182981957&amp;IncludeAdjustmentInvoices=false&amp;IsScheduling=True&amp;From=2026-03-28&amp;To=2027-03-27" display="View Report"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="hyperlinkId1" location="/new/reports/459565681?DateType=3&amp;BusinessUnitId=2415185%2C2415187%2C15775258%2C2415186%2C2415190%2C182981963%2C182981958%2C182981961%2C182981957&amp;IncludeAdjustmentInvoices=false&amp;IsScheduling=True&amp;From=2026-03-30&amp;To=2027-03-29" display="View Report"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/data/parts_report_future.xlsx
+++ b/data/parts_report_future.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6532c83e54804366"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="R9b2b33f7224f4bc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8b8a917c93874ee8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="R267d43cdfbaf499e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,29 +174,29 @@
         </x:is>
       </x:c>
       <x:c r="B2" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>710.85</x:v>
       </x:c>
       <x:c r="C2" t="inlineStr" s="7">
         <x:is>
-          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member</x:t>
+          <x:t>Gemaire, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D2" t="inlineStr" s="9">
         <x:is>
-          <x:t>587794082</x:t>
+          <x:t>580795172</x:t>
         </x:is>
       </x:c>
       <x:c r="E2" t="inlineStr" s="11">
         <x:is>
-          <x:t>587794082</x:t>
+          <x:t>580795172</x:t>
         </x:is>
       </x:c>
       <x:c r="F2" s="13">
-        <x:v>46111</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="G2" t="inlineStr" s="15">
         <x:is>
-          <x:t>Tyler Gallatin</x:t>
+          <x:t>PP Alejandro Espinosa</x:t>
         </x:is>
       </x:c>
       <x:c r="H2" t="inlineStr" s="17">
@@ -211,14 +211,14 @@
       </x:c>
       <x:c r="J2" t="inlineStr" s="21">
         <x:is>
-          <x:t>Louise Claydon</x:t>
+          <x:t>Paul Serota</x:t>
         </x:is>
       </x:c>
       <x:c r="K2" s="23">
-        <x:v>46110</x:v>
+        <x:v>46054</x:v>
       </x:c>
       <x:c r="L2" s="25">
-        <x:v>46110</x:v>
+        <x:v>46054</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -232,25 +232,25 @@
       </x:c>
       <x:c r="C3" t="inlineStr" s="7">
         <x:is>
-          <x:t>5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, 5 YEAR WARRANTY, Club Member 3 sys, Gemaire, MULTI- 3, Parts Ordered</x:t>
+          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D3" t="inlineStr" s="9">
         <x:is>
-          <x:t>586595677</x:t>
+          <x:t>554749130</x:t>
         </x:is>
       </x:c>
       <x:c r="E3" t="inlineStr" s="11">
         <x:is>
-          <x:t>586595677</x:t>
+          <x:t>554749130</x:t>
         </x:is>
       </x:c>
       <x:c r="F3" s="13">
-        <x:v>46111</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="G3" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
+          <x:t>Noel Richardson</x:t>
         </x:is>
       </x:c>
       <x:c r="H3" t="inlineStr" s="17">
@@ -260,19 +260,19 @@
       </x:c>
       <x:c r="I3" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J3" t="inlineStr" s="21">
         <x:is>
-          <x:t>Bob Lauson</x:t>
+          <x:t>Mildred Rousseau</x:t>
         </x:is>
       </x:c>
       <x:c r="K3" s="23">
-        <x:v>46098</x:v>
+        <x:v>45999</x:v>
       </x:c>
       <x:c r="L3" s="25">
-        <x:v>46098</x:v>
+        <x:v>45999</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -282,29 +282,29 @@
         </x:is>
       </x:c>
       <x:c r="B4" t="n" s="5">
-        <x:v>462.83</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C4" t="inlineStr" s="7">
         <x:is>
-          <x:t>Baker Supply, Club Member, Parts Ordered, PLM, Potential Membership Renewal, Residential Maintenance Agreement</x:t>
+          <x:t>Carrier enterprise, Club Member, Club Member 4 sys, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" t="inlineStr" s="9">
         <x:is>
-          <x:t>555552166</x:t>
+          <x:t>586668443</x:t>
         </x:is>
       </x:c>
       <x:c r="E4" t="inlineStr" s="11">
         <x:is>
-          <x:t>555552166</x:t>
+          <x:t>586668443</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" s="13">
-        <x:v>46111</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="G4" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Cesar Levy</x:t>
+          <x:t>Bruce Coe</x:t>
         </x:is>
       </x:c>
       <x:c r="H4" t="inlineStr" s="17">
@@ -314,19 +314,19 @@
       </x:c>
       <x:c r="I4" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J4" t="inlineStr" s="21">
         <x:is>
-          <x:t>Wanda Betancourt</x:t>
+          <x:t>Harry Leiby</x:t>
         </x:is>
       </x:c>
       <x:c r="K4" s="23">
-        <x:v>46007</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="L4" s="25">
-        <x:v>46007</x:v>
+        <x:v>46098</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -336,29 +336,29 @@
         </x:is>
       </x:c>
       <x:c r="B5" t="n" s="5">
-        <x:v>945.4</x:v>
+        <x:v>1536.7</x:v>
       </x:c>
       <x:c r="C5" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Received , PLM</x:t>
+          <x:t>Carrier enterprise, Parts Ordered, PLM</x:t>
         </x:is>
       </x:c>
       <x:c r="D5" t="inlineStr" s="9">
         <x:is>
-          <x:t>587403893</x:t>
+          <x:t>587489793</x:t>
         </x:is>
       </x:c>
       <x:c r="E5" t="inlineStr" s="11">
         <x:is>
-          <x:t>587403893</x:t>
+          <x:t>587489793</x:t>
         </x:is>
       </x:c>
       <x:c r="F5" s="13">
-        <x:v>46111</x:v>
+        <x:v>46113</x:v>
       </x:c>
       <x:c r="G5" t="inlineStr" s="15">
         <x:is>
-          <x:t>Rolin Moimeme</x:t>
+          <x:t>PP Tyriq McCall</x:t>
         </x:is>
       </x:c>
       <x:c r="H5" t="inlineStr" s="17">
@@ -373,14 +373,14 @@
       </x:c>
       <x:c r="J5" t="inlineStr" s="21">
         <x:is>
-          <x:t>WALKER, CAMERON</x:t>
+          <x:t>PASAMI, LLC</x:t>
         </x:is>
       </x:c>
       <x:c r="K5" s="23">
-        <x:v>46106</x:v>
+        <x:v>46107</x:v>
       </x:c>
       <x:c r="L5" s="25">
-        <x:v>46106</x:v>
+        <x:v>46107</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -394,25 +394,25 @@
       </x:c>
       <x:c r="C6" t="inlineStr" s="7">
         <x:is>
-          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D6" t="inlineStr" s="9">
         <x:is>
-          <x:t>463016698</x:t>
+          <x:t>478958137</x:t>
         </x:is>
       </x:c>
       <x:c r="E6" t="inlineStr" s="11">
         <x:is>
-          <x:t>463016698</x:t>
+          <x:t>478958137</x:t>
         </x:is>
       </x:c>
       <x:c r="F6" s="13">
-        <x:v>46111</x:v>
+        <x:v>46113</x:v>
       </x:c>
       <x:c r="G6" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Tyriq McCall</x:t>
+          <x:t>Ezekiel Mejia-Garcia</x:t>
         </x:is>
       </x:c>
       <x:c r="H6" t="inlineStr" s="17">
@@ -427,14 +427,14 @@
       </x:c>
       <x:c r="J6" t="inlineStr" s="21">
         <x:is>
-          <x:t>Evan Frangos</x:t>
+          <x:t>Sergio Bonadona</x:t>
         </x:is>
       </x:c>
       <x:c r="K6" s="23">
-        <x:v>45762</x:v>
+        <x:v>45864</x:v>
       </x:c>
       <x:c r="L6" s="25">
-        <x:v>45762</x:v>
+        <x:v>46106</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -444,29 +444,29 @@
         </x:is>
       </x:c>
       <x:c r="B7" t="n" s="5">
-        <x:v>303.45</x:v>
+        <x:v>1167.95</x:v>
       </x:c>
       <x:c r="C7" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, Potential Member</x:t>
+          <x:t>Carrier enterprise, Club Member 3 sys, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D7" t="inlineStr" s="9">
         <x:is>
-          <x:t>581332764</x:t>
+          <x:t>587208106</x:t>
         </x:is>
       </x:c>
       <x:c r="E7" t="inlineStr" s="11">
         <x:is>
-          <x:t>581332764</x:t>
+          <x:t>587208106</x:t>
         </x:is>
       </x:c>
       <x:c r="F7" s="13">
-        <x:v>46111</x:v>
+        <x:v>46115</x:v>
       </x:c>
       <x:c r="G7" t="inlineStr" s="15">
         <x:is>
-          <x:t>Justin Greene</x:t>
+          <x:t>Michael Kertesz </x:t>
         </x:is>
       </x:c>
       <x:c r="H7" t="inlineStr" s="17">
@@ -476,392 +476,68 @@
       </x:c>
       <x:c r="I7" t="inlineStr" s="19">
         <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
+          <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J7" t="inlineStr" s="21">
         <x:is>
-          <x:t>Chris Orsini</x:t>
+          <x:t>Brett Frankel</x:t>
         </x:is>
       </x:c>
       <x:c r="K7" s="23">
-        <x:v>46057</x:v>
+        <x:v>46104</x:v>
       </x:c>
       <x:c r="L7" s="25">
-        <x:v>46057</x:v>
+        <x:v>46104</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B8" t="n" s="5">
-        <x:v>710.85</x:v>
-      </x:c>
-      <x:c r="C8" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Gemaire, Parts Ordered, Potential Member</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8" t="inlineStr" s="9">
-        <x:is>
-          <x:t>580795172</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E8" t="inlineStr" s="11">
-        <x:is>
-          <x:t>580795172</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F8" s="13">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="G8" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H8" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I8" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J8" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Paul Serota</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K8" s="23">
-        <x:v>46054</x:v>
-      </x:c>
-      <x:c r="L8" s="25">
-        <x:v>46054</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B9" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C9" t="inlineStr" s="7">
-        <x:is>
-          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D9" t="inlineStr" s="9">
-        <x:is>
-          <x:t>554749130</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E9" t="inlineStr" s="11">
-        <x:is>
-          <x:t>554749130</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F9" s="13">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="G9" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Noel Richardson</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H9" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I9" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J9" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Mildred Rousseau</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K9" s="23">
-        <x:v>45999</x:v>
-      </x:c>
-      <x:c r="L9" s="25">
-        <x:v>45999</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B10" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C10" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Club Member, Club Member 4 sys, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D10" t="inlineStr" s="9">
-        <x:is>
-          <x:t>586668443</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E10" t="inlineStr" s="11">
-        <x:is>
-          <x:t>586668443</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F10" s="13">
-        <x:v>46112</x:v>
-      </x:c>
-      <x:c r="G10" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Bruce Coe</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H10" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I10" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J10" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Harry Leiby</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K10" s="23">
-        <x:v>46098</x:v>
-      </x:c>
-      <x:c r="L10" s="25">
-        <x:v>46098</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B11" t="n" s="5">
-        <x:v>1536.7</x:v>
-      </x:c>
-      <x:c r="C11" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, PLM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D11" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587489793</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E11" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587489793</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F11" s="13">
-        <x:v>46113</x:v>
-      </x:c>
-      <x:c r="G11" t="inlineStr" s="15">
-        <x:is>
-          <x:t>PP Tyriq McCall</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H11" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I11" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J11" t="inlineStr" s="21">
-        <x:is>
-          <x:t>PASAMI, LLC</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K11" s="23">
-        <x:v>46107</x:v>
-      </x:c>
-      <x:c r="L11" s="25">
-        <x:v>46107</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B12" t="n" s="5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C12" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D12" t="inlineStr" s="9">
-        <x:is>
-          <x:t>478958137</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E12" t="inlineStr" s="11">
-        <x:is>
-          <x:t>478958137</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F12" s="13">
-        <x:v>46113</x:v>
-      </x:c>
-      <x:c r="G12" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Ezekiel Mejia-Garcia</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H12" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I12" t="inlineStr" s="19">
-        <x:is>
-          <x:t>CS - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J12" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Sergio Bonadona</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K12" s="23">
-        <x:v>45864</x:v>
-      </x:c>
-      <x:c r="L12" s="25">
-        <x:v>46106</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="inlineStr" s="3">
-        <x:is>
-          <x:t>HC - Return to Repair</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B13" t="n" s="5">
-        <x:v>1167.95</x:v>
-      </x:c>
-      <x:c r="C13" t="inlineStr" s="7">
-        <x:is>
-          <x:t>Carrier enterprise, Club Member 3 sys, Parts Ordered</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D13" t="inlineStr" s="9">
-        <x:is>
-          <x:t>587208106</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E13" t="inlineStr" s="11">
-        <x:is>
-          <x:t>587208106</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F13" s="13">
-        <x:v>46115</x:v>
-      </x:c>
-      <x:c r="G13" t="inlineStr" s="15">
-        <x:is>
-          <x:t>Michael Kertesz </x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H13" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I13" t="inlineStr" s="19">
-        <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J13" t="inlineStr" s="21">
-        <x:is>
-          <x:t>Brett Frankel</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K13" s="23">
-        <x:v>46104</x:v>
-      </x:c>
-      <x:c r="L13" s="25">
-        <x:v>46104</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="n" s="4">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B14" t="n" s="6">
-        <x:v>427.265</x:v>
-      </x:c>
-      <x:c r="C14" t="inlineStr" s="8">
+      <x:c r="A8" t="n" s="4">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B8" t="n" s="6">
+        <x:v>569.25</x:v>
+      </x:c>
+      <x:c r="C8" t="inlineStr" s="8">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D14" t="n" s="10">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E14" t="inlineStr" s="12">
+      <x:c r="D8" t="n" s="10">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E8" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F14" s="14">
+      <x:c r="F8" s="14">
         <x:v/>
       </x:c>
-      <x:c r="G14" t="inlineStr" s="16">
+      <x:c r="G8" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H14" t="inlineStr" s="18">
+      <x:c r="H8" t="inlineStr" s="18">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="I14" t="inlineStr" s="20">
+      <x:c r="I8" t="inlineStr" s="20">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="J14" t="inlineStr" s="22">
+      <x:c r="J8" t="inlineStr" s="22">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="K14" s="24">
+      <x:c r="K8" s="24">
         <x:v/>
       </x:c>
-      <x:c r="L14" s="26">
+      <x:c r="L8" s="26">
         <x:v/>
       </x:c>
     </x:row>
@@ -892,7 +568,7 @@
       </x:c>
       <x:c r="B2" t="inlineStr" s="28">
         <x:is>
-          <x:t>03/30/26 - 03/29/27</x:t>
+          <x:t>03/31/26 - 03/30/27</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -958,7 +634,7 @@
     <x:mergeCell ref="A8:B8"/>
   </x:mergeCells>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="hyperlinkId1" location="/new/reports/459565681?DateType=3&amp;BusinessUnitId=2415185%2C2415187%2C15775258%2C2415186%2C2415190%2C182981963%2C182981958%2C182981961%2C182981957&amp;IncludeAdjustmentInvoices=false&amp;IsScheduling=True&amp;From=2026-03-30&amp;To=2027-03-29" display="View Report"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="hyperlinkId1" location="/new/reports/459565681?DateType=3&amp;BusinessUnitId=2415185%2C2415187%2C15775258%2C2415186%2C2415190%2C182981963%2C182981958%2C182981961%2C182981957&amp;IncludeAdjustmentInvoices=false&amp;IsScheduling=True&amp;From=2026-03-31&amp;To=2027-03-30" display="View Report"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/data/parts_report_future.xlsx
+++ b/data/parts_report_future.xlsx
@@ -5,8 +5,8 @@
     <x:workbookView/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8b8a917c93874ee8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="R267d43cdfbaf499e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R20948534ddcd4a3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filters" sheetId="2" r:id="Rc9dd33eb69ae4665"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,21 +174,21 @@
         </x:is>
       </x:c>
       <x:c r="B2" t="n" s="5">
-        <x:v>710.85</x:v>
+        <x:v>610.85</x:v>
       </x:c>
       <x:c r="C2" t="inlineStr" s="7">
         <x:is>
-          <x:t>Gemaire, Parts Ordered, Potential Member</x:t>
+          <x:t>10-10-10, Club Member, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D2" t="inlineStr" s="9">
         <x:is>
-          <x:t>580795172</x:t>
+          <x:t>587680855</x:t>
         </x:is>
       </x:c>
       <x:c r="E2" t="inlineStr" s="11">
         <x:is>
-          <x:t>580795172</x:t>
+          <x:t>587680855</x:t>
         </x:is>
       </x:c>
       <x:c r="F2" s="13">
@@ -196,7 +196,7 @@
       </x:c>
       <x:c r="G2" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Alejandro Espinosa</x:t>
+          <x:t>PP Martin Ebanks</x:t>
         </x:is>
       </x:c>
       <x:c r="H2" t="inlineStr" s="17">
@@ -211,14 +211,14 @@
       </x:c>
       <x:c r="J2" t="inlineStr" s="21">
         <x:is>
-          <x:t>Paul Serota</x:t>
+          <x:t>Lester  Mena</x:t>
         </x:is>
       </x:c>
       <x:c r="K2" s="23">
-        <x:v>46054</x:v>
+        <x:v>46108</x:v>
       </x:c>
       <x:c r="L2" s="25">
-        <x:v>46054</x:v>
+        <x:v>46108</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -228,21 +228,21 @@
         </x:is>
       </x:c>
       <x:c r="B3" t="n" s="5">
-        <x:v>0</x:v>
+        <x:v>710.85</x:v>
       </x:c>
       <x:c r="C3" t="inlineStr" s="7">
         <x:is>
-          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
+          <x:t>Gemaire, Parts Ordered, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D3" t="inlineStr" s="9">
         <x:is>
-          <x:t>554749130</x:t>
+          <x:t>580795172</x:t>
         </x:is>
       </x:c>
       <x:c r="E3" t="inlineStr" s="11">
         <x:is>
-          <x:t>554749130</x:t>
+          <x:t>580795172</x:t>
         </x:is>
       </x:c>
       <x:c r="F3" s="13">
@@ -250,7 +250,7 @@
       </x:c>
       <x:c r="G3" t="inlineStr" s="15">
         <x:is>
-          <x:t>Noel Richardson</x:t>
+          <x:t>PP Alejandro Espinosa</x:t>
         </x:is>
       </x:c>
       <x:c r="H3" t="inlineStr" s="17">
@@ -265,14 +265,14 @@
       </x:c>
       <x:c r="J3" t="inlineStr" s="21">
         <x:is>
-          <x:t>Mildred Rousseau</x:t>
+          <x:t>Paul Serota</x:t>
         </x:is>
       </x:c>
       <x:c r="K3" s="23">
-        <x:v>45999</x:v>
+        <x:v>46054</x:v>
       </x:c>
       <x:c r="L3" s="25">
-        <x:v>45999</x:v>
+        <x:v>46054</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -286,17 +286,17 @@
       </x:c>
       <x:c r="C4" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Club Member 4 sys, Parts Ordered</x:t>
+          <x:t>10-10-10, 10-10-10, 10-10-10, 10-10-10, Carrier enterprise, Club Member, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D4" t="inlineStr" s="9">
         <x:is>
-          <x:t>586668443</x:t>
+          <x:t>554749130</x:t>
         </x:is>
       </x:c>
       <x:c r="E4" t="inlineStr" s="11">
         <x:is>
-          <x:t>586668443</x:t>
+          <x:t>554749130</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" s="13">
@@ -304,7 +304,7 @@
       </x:c>
       <x:c r="G4" t="inlineStr" s="15">
         <x:is>
-          <x:t>Bruce Coe</x:t>
+          <x:t>Noel Richardson</x:t>
         </x:is>
       </x:c>
       <x:c r="H4" t="inlineStr" s="17">
@@ -319,14 +319,14 @@
       </x:c>
       <x:c r="J4" t="inlineStr" s="21">
         <x:is>
-          <x:t>Harry Leiby</x:t>
+          <x:t>Mildred Rousseau</x:t>
         </x:is>
       </x:c>
       <x:c r="K4" s="23">
-        <x:v>46098</x:v>
+        <x:v>45999</x:v>
       </x:c>
       <x:c r="L4" s="25">
-        <x:v>46098</x:v>
+        <x:v>45999</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -336,29 +336,29 @@
         </x:is>
       </x:c>
       <x:c r="B5" t="n" s="5">
-        <x:v>1536.7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C5" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Parts Ordered, PLM</x:t>
+          <x:t>Carrier enterprise, Club Member, Club Member 4 sys, Parts Ordered</x:t>
         </x:is>
       </x:c>
       <x:c r="D5" t="inlineStr" s="9">
         <x:is>
-          <x:t>587489793</x:t>
+          <x:t>586668443</x:t>
         </x:is>
       </x:c>
       <x:c r="E5" t="inlineStr" s="11">
         <x:is>
-          <x:t>587489793</x:t>
+          <x:t>586668443</x:t>
         </x:is>
       </x:c>
       <x:c r="F5" s="13">
-        <x:v>46113</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="G5" t="inlineStr" s="15">
         <x:is>
-          <x:t>PP Tyriq McCall</x:t>
+          <x:t>Bruce Coe</x:t>
         </x:is>
       </x:c>
       <x:c r="H5" t="inlineStr" s="17">
@@ -368,19 +368,19 @@
       </x:c>
       <x:c r="I5" t="inlineStr" s="19">
         <x:is>
-          <x:t>PLM - HVAC - Service - 12</x:t>
+          <x:t>CS - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
       <x:c r="J5" t="inlineStr" s="21">
         <x:is>
-          <x:t>PASAMI, LLC</x:t>
+          <x:t>Harry Leiby</x:t>
         </x:is>
       </x:c>
       <x:c r="K5" s="23">
-        <x:v>46107</x:v>
+        <x:v>46098</x:v>
       </x:c>
       <x:c r="L5" s="25">
-        <x:v>46107</x:v>
+        <x:v>46098</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -394,25 +394,25 @@
       </x:c>
       <x:c r="C6" t="inlineStr" s="7">
         <x:is>
-          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
+          <x:t>Carrier enterprise, Parts Ordered, PLM, Potential Member</x:t>
         </x:is>
       </x:c>
       <x:c r="D6" t="inlineStr" s="9">
         <x:is>
-          <x:t>478958137</x:t>
+          <x:t>583259145</x:t>
         </x:is>
       </x:c>
       <x:c r="E6" t="inlineStr" s="11">
         <x:is>
-          <x:t>478958137</x:t>
+          <x:t>583259145</x:t>
         </x:is>
       </x:c>
       <x:c r="F6" s="13">
-        <x:v>46113</x:v>
+        <x:v>46112</x:v>
       </x:c>
       <x:c r="G6" t="inlineStr" s="15">
         <x:is>
-          <x:t>Ezekiel Mejia-Garcia</x:t>
+          <x:t/>
         </x:is>
       </x:c>
       <x:c r="H6" t="inlineStr" s="17">
@@ -427,14 +427,14 @@
       </x:c>
       <x:c r="J6" t="inlineStr" s="21">
         <x:is>
-          <x:t>Sergio Bonadona</x:t>
+          <x:t>John Moore</x:t>
         </x:is>
       </x:c>
       <x:c r="K6" s="23">
-        <x:v>45864</x:v>
+        <x:v>46070</x:v>
       </x:c>
       <x:c r="L6" s="25">
-        <x:v>46106</x:v>
+        <x:v>46070</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -444,100 +444,748 @@
         </x:is>
       </x:c>
       <x:c r="B7" t="n" s="5">
+        <x:v>2118</x:v>
+      </x:c>
+      <x:c r="C7" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Carrier enterprise, Parts Ordered, Potential Member, Replacement Opportunity</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587767849</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E7" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587767849</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F7" s="13">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="G7" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Michael Donnauro</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H7" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I7" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J7" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Diomicira Zecchino</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K7" s="23">
+        <x:v>46109</x:v>
+      </x:c>
+      <x:c r="L7" s="25">
+        <x:v>46109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" t="n" s="5">
+        <x:v>294.96</x:v>
+      </x:c>
+      <x:c r="C8" t="inlineStr" s="7">
+        <x:is>
+          <x:t>10-10-10, 10-10-10, Club Member, Club Member (Additional System), MULTI- 2, Parts Ordered, Trane Supply</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D8" t="inlineStr" s="9">
+        <x:is>
+          <x:t>554624809</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E8" t="inlineStr" s="11">
+        <x:is>
+          <x:t>554624809</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F8" s="13">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="G8" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Carlos Machado</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H8" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I8" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J8" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Michael &amp; Delle Lenzen</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K8" s="23">
+        <x:v>45996</x:v>
+      </x:c>
+      <x:c r="L8" s="25">
+        <x:v>45996</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" t="n" s="5">
+        <x:v>810.22</x:v>
+      </x:c>
+      <x:c r="C9" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Club Member, Gemaire, Parts Ordered</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587761129</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E9" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587761129</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F9" s="13">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="G9" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Rolin Moimeme</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H9" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I9" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J9" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Nancy Brown</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K9" s="23">
+        <x:v>46109</x:v>
+      </x:c>
+      <x:c r="L9" s="25">
+        <x:v>46109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" t="n" s="5">
+        <x:v>2022</x:v>
+      </x:c>
+      <x:c r="C10" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Parts Ordered, Potential Member, Trane Supply</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D10" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587751042</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E10" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587751042</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F10" s="13">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="G10" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Rickey McClam </x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H10" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I10" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J10" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Andy Ong</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K10" s="23">
+        <x:v>46109</x:v>
+      </x:c>
+      <x:c r="L10" s="25">
+        <x:v>46109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" t="n" s="5">
+        <x:v>1536.7</x:v>
+      </x:c>
+      <x:c r="C11" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Carrier enterprise, Parts Ordered, PLM</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D11" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587489793</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E11" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587489793</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F11" s="13">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="G11" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Tyriq McCall</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H11" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I11" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J11" t="inlineStr" s="21">
+        <x:is>
+          <x:t>PASAMI, LLC</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K11" s="23">
+        <x:v>46107</x:v>
+      </x:c>
+      <x:c r="L11" s="25">
+        <x:v>46107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C12" t="inlineStr" s="7">
+        <x:is>
+          <x:t>5-YR Labor Warranty, 5-YR Labor Warranty, 5-YR Labor Warranty, 5-YR Labor Warranty, Goodman distribution , Parts Ordered, Potential Member</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587806192</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587806192</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F12" s="13">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="G12" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Bruce Coe</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H12" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I12" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J12" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Maria Hill</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K12" s="23">
+        <x:v>46111</x:v>
+      </x:c>
+      <x:c r="L12" s="25">
+        <x:v>46111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C13" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Carrier enterprise, Club Member, Parts Ordered</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D13" t="inlineStr" s="9">
+        <x:is>
+          <x:t>478958137</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E13" t="inlineStr" s="11">
+        <x:is>
+          <x:t>478958137</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F13" s="13">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="G13" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Ezekiel Mejia-Garcia</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H13" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I13" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J13" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Sergio Bonadona</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K13" s="23">
+        <x:v>45864</x:v>
+      </x:c>
+      <x:c r="L13" s="25">
+        <x:v>46106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" t="n" s="5">
+        <x:v>579.81</x:v>
+      </x:c>
+      <x:c r="C14" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Club Member, Parts Ordered, Replacement Opportunity, Trane Supply</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587764352</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E14" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587764352</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F14" s="13">
+        <x:v>46114</x:v>
+      </x:c>
+      <x:c r="G14" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Barrington Wilson</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H14" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I14" t="inlineStr" s="19">
+        <x:is>
+          <x:t>CS - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J14" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Edna Parkin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K14" s="23">
+        <x:v>46109</x:v>
+      </x:c>
+      <x:c r="L14" s="25">
+        <x:v>46109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15" t="n" s="5">
+        <x:v>1883</x:v>
+      </x:c>
+      <x:c r="C15" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Gemaire, NO AIR, Parts Ordered, PLM, Potential Member</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587796621</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E15" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587796621</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F15" s="13">
+        <x:v>46114</x:v>
+      </x:c>
+      <x:c r="G15" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Jesse Dague</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H15" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I15" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J15" t="inlineStr" s="21">
+        <x:is>
+          <x:t>BONCZEK, TIM</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K15" s="23">
+        <x:v>46110</x:v>
+      </x:c>
+      <x:c r="L15" s="25">
+        <x:v>46110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B16" t="n" s="5">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="C16" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Carrier enterprise, Club Member 3 sys, MULTI- 3, Parts Ordered, PLM, Replacement Opportunity</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D16" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587789020</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E16" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587789020</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F16" s="13">
+        <x:v>46114</x:v>
+      </x:c>
+      <x:c r="G16" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Anthony Capalbo</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H16" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I16" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J16" t="inlineStr" s="21">
+        <x:is>
+          <x:t>HARRIS, MIKE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K16" s="23">
+        <x:v>46110</x:v>
+      </x:c>
+      <x:c r="L16" s="25">
+        <x:v>46110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B17" t="n" s="5">
+        <x:v>2405.92</x:v>
+      </x:c>
+      <x:c r="C17" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Baker Supply, Parts Ordered, Potential Member</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" t="inlineStr" s="9">
+        <x:is>
+          <x:t>578394047</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E17" t="inlineStr" s="11">
+        <x:is>
+          <x:t>578394047</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F17" s="13">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="G17" t="inlineStr" s="15">
+        <x:is>
+          <x:t>PP Gurpreet Parihar</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H17" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I17" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J17" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Edgar Irving</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K17" s="23">
+        <x:v>46036</x:v>
+      </x:c>
+      <x:c r="L17" s="25">
+        <x:v>46036</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B18" t="n" s="5">
         <x:v>1167.95</x:v>
       </x:c>
-      <x:c r="C7" t="inlineStr" s="7">
+      <x:c r="C18" t="inlineStr" s="7">
         <x:is>
           <x:t>Carrier enterprise, Club Member 3 sys, Parts Ordered</x:t>
         </x:is>
       </x:c>
-      <x:c r="D7" t="inlineStr" s="9">
+      <x:c r="D18" t="inlineStr" s="9">
         <x:is>
           <x:t>587208106</x:t>
         </x:is>
       </x:c>
-      <x:c r="E7" t="inlineStr" s="11">
+      <x:c r="E18" t="inlineStr" s="11">
         <x:is>
           <x:t>587208106</x:t>
         </x:is>
       </x:c>
-      <x:c r="F7" s="13">
+      <x:c r="F18" s="13">
         <x:v>46115</x:v>
       </x:c>
-      <x:c r="G7" t="inlineStr" s="15">
+      <x:c r="G18" t="inlineStr" s="15">
         <x:is>
           <x:t>Michael Kertesz </x:t>
         </x:is>
       </x:c>
-      <x:c r="H7" t="inlineStr" s="17">
-        <x:is>
-          <x:t>Hold</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I7" t="inlineStr" s="19">
+      <x:c r="H18" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I18" t="inlineStr" s="19">
         <x:is>
           <x:t>PLM - HVAC - Service - 12</x:t>
         </x:is>
       </x:c>
-      <x:c r="J7" t="inlineStr" s="21">
+      <x:c r="J18" t="inlineStr" s="21">
         <x:is>
           <x:t>Brett Frankel</x:t>
         </x:is>
       </x:c>
-      <x:c r="K7" s="23">
+      <x:c r="K18" s="23">
         <x:v>46104</x:v>
       </x:c>
-      <x:c r="L7" s="25">
+      <x:c r="L18" s="25">
         <x:v>46104</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="n" s="4">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B8" t="n" s="6">
-        <x:v>569.25</x:v>
-      </x:c>
-      <x:c r="C8" t="inlineStr" s="8">
+    <x:row r="19">
+      <x:c r="A19" t="inlineStr" s="3">
+        <x:is>
+          <x:t>HC - Return to Repair</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B19" t="n" s="5">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C19" t="inlineStr" s="7">
+        <x:is>
+          <x:t>Carrier enterprise, Club Member, Parts Ordered, PLM</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D19" t="inlineStr" s="9">
+        <x:is>
+          <x:t>587785435</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E19" t="inlineStr" s="11">
+        <x:is>
+          <x:t>587785435</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F19" s="13">
+        <x:v>46125</x:v>
+      </x:c>
+      <x:c r="G19" t="inlineStr" s="15">
+        <x:is>
+          <x:t>Tyler Gallatin</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H19" t="inlineStr" s="17">
+        <x:is>
+          <x:t>Hold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I19" t="inlineStr" s="19">
+        <x:is>
+          <x:t>PLM - HVAC - Service - 12</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J19" t="inlineStr" s="21">
+        <x:is>
+          <x:t>Lera Chacon</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K19" s="23">
+        <x:v>46110</x:v>
+      </x:c>
+      <x:c r="L19" s="25">
+        <x:v>46110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="n" s="4">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B20" t="n" s="6">
+        <x:v>815.0144444444444444444444444</x:v>
+      </x:c>
+      <x:c r="C20" t="inlineStr" s="8">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="D8" t="n" s="10">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E8" t="inlineStr" s="12">
+      <x:c r="D20" t="n" s="10">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E20" t="inlineStr" s="12">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="F8" s="14">
+      <x:c r="F20" s="14">
         <x:v/>
       </x:c>
-      <x:c r="G8" t="inlineStr" s="16">
+      <x:c r="G20" t="inlineStr" s="16">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="H8" t="inlineStr" s="18">
+      <x:c r="H20" t="inlineStr" s="18">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="I8" t="inlineStr" s="20">
+      <x:c r="I20" t="inlineStr" s="20">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="J8" t="inlineStr" s="22">
+      <x:c r="J20" t="inlineStr" s="22">
         <x:is>
           <x:t/>
         </x:is>
       </x:c>
-      <x:c r="K8" s="24">
+      <x:c r="K20" s="24">
         <x:v/>
       </x:c>
-      <x:c r="L8" s="26">
+      <x:c r="L20" s="26">
         <x:v/>
       </x:c>
     </x:row>
